--- a/interconnections_datasets_auth/bibtex_mapping_of_ids_authentication.xlsx
+++ b/interconnections_datasets_auth/bibtex_mapping_of_ids_authentication.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="56">
   <si>
     <t>ID</t>
   </si>
@@ -614,6 +614,295 @@
 	keywords = {Ear, Irrigation, Authentication, Electroencephalography, Biometrics, Shape, Microphones, Acoustics, authentication, active acoustic sensing, ear biometrics, Hearables, Legged locomotion, Mobile computing, sound leakage},
 	pages = {6183--6196},
 	file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\6V24CG7D\\Amesaka et al. - 2025 - EarLock Personal Authentication System for Hearables Using Sound Leakage Signals.pdf:application/pdf},
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@article{wang_eardynamic_2021,
+ title = {{EarDynamic}: {An} {Ear} {Canal} {Deformation} {Based} {Continuous} {User} {Authentication} {Using} {In}-{Ear} {Wearables}},
+ volume = {5},
+ shorttitle = {{EarDynamic}},
+ url = {https://dl.acm.org/doi/10.1145/3448098},
+ doi = {10.1145/3448098},
+ abstract = {Biometric-based authentication is gaining increasing attention for wearables and mobile applications. Meanwhile, the growing adoption of sensors in wearables also provides opportunities to capture novel wearable biometrics. In this work, we propose EarDynamic, an ear canal deformation based user authentication using in-ear wearables. EarDynamic provides continuous and passive user authentication and is transparent to users. It leverages ear canal deformation that combines the unique static geometry and dynamic motions of the ear canal when the user is speaking for authentication. It utilizes an acoustic sensing approach to capture the ear canal deformation with the built-in microphone and speaker of the in-ear wearable. Specifically, it first emits well-designed inaudible beep signals and records the reflected signals from the ear canal. It then analyzes the reflected signals and extracts fine-grained acoustic features that correspond to the ear canal deformation for user authentication. Our extensive experimental evaluation shows that EarDynamic can achieve a recall of 97.38\% and an F1 score of 96.84\%. Results also show that our system works well under different noisy environments with various daily activities.},
+ number = {1},
+ urldate = {2026-01-16},
+ journal = {Proc. ACM Interact. Mob. Wearable Ubiquitous Technol.},
+ author = {Wang, Zi and Tan, Sheng and Zhang, Linghan and Ren, Yili and Wang, Zhi and Yang, Jie},
+ year = {2021},
+ pages = {39:1--39:27},
+ file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\H68YIYBM\\Wang et al. - 2021 - EarDynamic An Ear Canal Deformation Based Continuous User Authentication Using In-Ear Wearables.pdf:application/pdf},
+}
+</t>
+  </si>
+  <si>
+    <t>@article{nakamura_-ear_2018,
+ title = {In-{Ear} {EEG} {Biometrics} for {Feasible} and {Readily} {Collectable} {Real}-{World} {Person} {Authentication}},
+ volume = {13},
+ issn = {1556-6021},
+ url = {https://ieeexplore.ieee.org/document/8067531},
+ doi = {10.1109/TIFS.2017.2763124},
+ abstract = {The use of electroencephalogram (EEG) as a biometrics modality has been investigated for about a decade; however, its feasibility in real-world applications is not yet conclusively established, mainly due to the issues with collectability and reproducibility. To this end, we propose a readily deployable EEG biometrics system based on a “one-fits-all” viscoelastic generic in-ear EEG sensor (collectability), which does not require skilled assistance or cumbersome preparation. Unlike most existing studies, we consider data recorded over multiple recording days and for multiple subjects (reproducibility) while, for rigour, the training and test segments are not taken from the same recording days. A robust approach is considered based on the resting state with eyes closed paradigm, the use of both parametric (autoregressive model) and non-parametric (spectral) features, and supported by simple and fast cosine distance, linear discriminant analysis, and support vector machine classifiers. Both the verification and identification forensics scenarios are considered and the achieved results are on par with the studies based on impractical on-scalp recordings. Comprehensive analysis over a number of subjects, setups, and analysis features demonstrates the feasibility of the proposed ear-EEG biometrics, and its potential in resolving the critical collectability, robustness, and reproducibility issues associated with current EEG biometrics.},
+ number = {3},
+ urldate = {2026-01-16},
+ journal = {IEEE Transactions on Information Forensics and Security},
+ author = {Nakamura, Takashi and Goverdovsky, Valentin and Mandic, Danilo P.},
+ month = mar,
+ year = {2018},
+ keywords = {Authentication, biometrics, electroencephalography, Electroencephalography, Feature extraction, Iris recognition, Robustness, Training, Wearable sensors},
+ pages = {648--661},
+ file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\2WC53Z89\\Nakamura et al. - 2018 - In-Ear EEG Biometrics for Feasible and Readily Collectable Real-World Person Authentication.pdf:application/pdf},
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@inproceedings{mahto_ear_2018,
+ title = {Ear {Acoustic} {Biometrics} {Using} {Inaudible} {Signals} and {Its} {Application} to {Continuous} {User} {Authentication}},
+ issn = {2076-1465},
+ url = {https://ieeexplore.ieee.org/document/8553015},
+ doi = {10.23919/EUSIPCO.2018.8553015},
+ abstract = {This paper presents an improved version of a previously-proposed ear-acoustic biometric system for personal authentication. Even though the previous system provided a fast, accurate, and easy means of authentication, it employed noticeably audible probe signals to extract ear acoustic-features, signals which might interrupt user activities. To overcome this problem, this paper presents silent user authentication by employing inaudible signals in the place of audible signals for capturing ear acoustic-features. A comparative study using a number of audible and inaudible signals demonstrates that inaudible signals provide accurate authentication under the condition that the relative position of the earphone device against the ear canal is constant, which is a requirement for continuous user authentication. On the other hand, audible signals offer better accuracy when the earphone position changes, which is often the case in initial user authentication. This suggests the idea of a hybrid system that employs both audible and inaudible signals for, respectively, accurate initial authentication and user-friendly continuous authentication.},
+ urldate = {2026-01-16},
+ booktitle = {2018 26th {European} {Signal} {Processing} {Conference} ({EUSIPCO})},
+ author = {Mahto, Shivangi and Arakawa, Takayuki and Koshinak, Takafumi},
+ month = sep,
+ year = {2018},
+ note = {ISSN: 2076-1465},
+ keywords = {Ear, Irrigation, Authentication, Headphones, Biometrics (access control), Acoustics, Probes},
+ pages = {1407--1411},
+ file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\M7NPRWG8\\Mahto et al. - 2018 - Ear Acoustic Biometrics Using Inaudible Signals and Its Application to Continuous User Authenticatio.pdf:application/pdf},
+}
+</t>
+  </si>
+  <si>
+    <t>@article{liu_earprint_2014,
+ title = {Earprint: {Transient} {Evoked} {Otoacoustic} {Emission} for {Biometrics}},
+ volume = {9},
+ issn = {1556-6021},
+ shorttitle = {Earprint},
+ url = {https://ieeexplore.ieee.org/document/6914592},
+ doi = {10.1109/TIFS.2014.2361205},
+ abstract = {Biometrics is attracting increasing attention in privacy and security concerned issues, such as access control and remote financial transaction. However, advanced forgery and spoofing techniques are threatening the reliability of conventional biometric modalities. This has been motivating our investigation of a novel yet promising modality transient evoked otoacoustic emission (TEOAE), which is an acoustic response generated from cochlea after a click stimulus. Unlike conventional modalities that are easily accessible or captured, TEOAE is naturally immune to replay and falsification attacks as a physiological outcome from human auditory system. In this paper, we resort to wavelet analysis to derive the time-frequency representation of such nonstationary signal, which reveals individual uniqueness and long-term reproducibility. A machine learning technique linear discriminant analysis is subsequently utilized to reduce intrasubject variability and further capture intersubject differentiation features. Considering practical application, we also introduce a complete framework of the biometric system in both verification and identification modes. Comparative experiments on a TEOAE data set of biometric setting show the merits of the proposed method. Performance is further improved with fusion of information from both ears.},
+ number = {12},
+ urldate = {2026-01-16},
+ journal = {IEEE Transactions on Information Forensics and Security},
+ author = {Liu, Yuxi and Hatzinakos, Dimitrios},
+ month = dec,
+ year = {2014},
+ keywords = {Feature extraction, Biometrics (access control), Auditory system, biometric fusion, linear discriminant analysis, Linear discriminant analysis, Robust biometric modality, Robust Biometric Modality, time-frequency analysis, Time-frequency analysis, Time-frequency Analysis, transient evoked otoacoustic emission, Transient Evoked Otoacoustic Emission},
+ pages = {2291--2301},
+ file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\ST468TL4\\Liu and Hatzinakos - 2014 - Earprint Transient Evoked Otoacoustic Emission for Biometrics.pdf:application/pdf},
+}</t>
+  </si>
+  <si>
+    <t>@inproceedings{liu_mandipass_2021,
+ title = {{MandiPass}: {Secure} and {Usable} {User} {Authentication} via {Earphone} {IMU}},
+ issn = {2575-8411},
+ shorttitle = {{MandiPass}},
+ url = {https://ieeexplore.ieee.org/abstract/document/9546415},
+ doi = {10.1109/ICDCS51616.2021.00070},
+ abstract = {Biometric plays an important role in user authentication. However, the most widely used biometrics, such as facial feature and fingerprint, are easy to capture or record, and thus vulnerable to spoofing attacks. On the contrary, intracorporal biometrics, such as electrocardiography and electroencephalography, are hard to collect, and hence more secure for authentication. Unfortunately, adopting them is not user-friendly due to their complicated collection methods and inconvenient constraints on users. In this paper, we propose a novel biometric-based authentication system, namely MandiPass. MandiPass leverages inertial measurement units (IMU), which have been widely deployed in portable devices, to collect intracorporal biometric from the vibration of user's mandible. The authentication merely requires user to voice a short ‘EMM’ for generating the vibration. In this way, MandiPass enables a secure and user-friendly biometric-based authentication. We theoretically validate the feasibility of MandiPass and develop a two-branch deep neural network for effective biometric extraction. We also utilize a Gaussian matrix to defend against replay attacks. Extensive experiment results with 34 volunteers show that MandiPass can achieve an equal error rate of 1.28\%, even under various harsh environments.},
+ urldate = {2026-01-16},
+ booktitle = {2021 {IEEE} 41st {International} {Conference} on {Distributed} {Computing} {Systems} ({ICDCS})},
+ author = {Liu, Jianwei and Song, Wenfan and Shen, Leming and Han, Jinsong and Xu, Xian and Ren, Kui},
+ month = jul,
+ year = {2021},
+ note = {ISSN: 2575-8411},
+ keywords = {Authentication, Biometrics, Headphones, Deep learning, Biometrics (access control), Vibrations, User Authentication, Deep Learning, Error analysis, Inertial Measurement Unit, Measurement units},
+ pages = {674--684},
+ file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\WAFDGKMI\\Liu et al. - 2021 - MandiPass Secure and Usable User Authentication via Earphone IMU.pdf:application/pdf},
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@article{gao_earecho_2019,
+ title = {{EarEcho}: {Using} {Ear} {Canal} {Echo} for {Wearable} {Authentication}},
+ volume = {3},
+ shorttitle = {{EarEcho}},
+ url = {https://dl.acm.org/doi/10.1145/3351239},
+ doi = {10.1145/3351239},
+ abstract = {Smart wearable devices have recently become one of the major technological trends and been widely adopted by the general public. Wireless earphones, in particular, have seen a skyrocketing growth due to its great usability and convenience. With the goal of seeking a more unobtrusive wearable authentication method that the users can easily use and conveniently access, in this study we present EarEcho as a novel, affordable, user-friendly biometric authentication solution. EarEcho takes advantages of the unique physical and geometrical characteristics of human ear canal and assesses the content-free acoustic features of in-ear sound waves for user authentication in a wearable and mobile manner. We implemented the proposed EarEcho on a proof-of-concept prototype and tested it among 20 subjects under diverse application scenarios. We can achieve a recall of 94.19\% and precision of 95.16\% for one-time authentication, while a recall of 97.55\% and precision of 97.57\% for continuous authentication. EarEcho has demonstrated its stability over time and robustness to cope with the uncertainties on the varying background noises, body motions, and sound pressure levels.},
+ number = {3},
+ urldate = {2026-01-16},
+ journal = {Proc. ACM Interact. Mob. Wearable Ubiquitous Technol.},
+ author = {Gao, Yang and Wang, Wei and Phoha, Vir V. and Sun, Wei and Jin, Zhanpeng},
+ year = {2019},
+ pages = {81:1--81:24},
+ file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\FHMS8BMN\\Gao et al. - 2019 - EarEcho Using Ear Canal Echo for Wearable Authentication.pdf:application/pdf},
+}
+</t>
+  </si>
+  <si>
+    <t>@article{gao_voice_2021,
+ title = {Voice {In} {Ear}: {Spoofing}-{Resistant} and {Passphrase}-{Independent} {Body} {Sound} {Authentication}},
+ volume = {5},
+ shorttitle = {Voice {In} {Ear}},
+ url = {https://dl.acm.org/doi/10.1145/3448113},
+ doi = {10.1145/3448113},
+ abstract = {With the rapid growth of wearable computing and increasing demand for mobile authentication scenarios, voiceprint-based authentication has become one of the prevalent technologies and has already presented tremendous potentials to the public. However, it is vulnerable to voice spoofing attacks (e.g., replay attacks and synthetic voice attacks). To address this threat, we propose a new biometric authentication approach, named EarPrint, which aims to extend voiceprint and build a hidden and secure user authentication scheme on earphones. EarPrint builds on the speaking-induced body sound transmission from the throat to the ear canal, i.e., different users will have different body sound conduction patterns on both sides of ears. As the first exploratory study, extensive experiments on 23 subjects show the EarPrint is robust against ambient noises and body motions. EarPrint achieves an Equal Error Rate (EER) of 3.64\% with 75 seconds enrollment data. We also evaluate the resilience of EarPrint against replay attacks. A major contribution of EarPrint is that it leverages two-level uniqueness, including the body sound conduction from the throat to the ear canal and the body asymmetry between the left and the right ears, taking advantage of earphones' paring form-factor. Compared with other mobile and wearable biometric modalities, EarPrint is a low-cost, accurate, and secure authentication solution for earphone users.},
+ number = {1},
+ urldate = {2026-01-16},
+ journal = {Proc. ACM Interact. Mob. Wearable Ubiquitous Technol.},
+ author = {Gao, Yang and Jin, Yincheng and Chauhan, Jagmohan and Choi, Seokmin and Li, Jiyang and Jin, Zhanpeng},
+ year = {2021},
+ pages = {12:1--12:25},
+ file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\AWX5L2ZX\\Gao et al. - 2021 - Voice In Ear Spoofing-Resistant and Passphrase-Independent Body Sound Authentication.pdf:application/pdf},
+}</t>
+  </si>
+  <si>
+    <t>@inproceedings{ferlini_eargate_2021,
+ address = {New York, NY, USA},
+ series = {{MobiCom} '21},
+ title = {{EarGate}: gait-based user identification with in-ear microphones},
+ isbn = {978-1-4503-8342-4},
+ shorttitle = {{EarGate}},
+ url = {https://dl.acm.org/doi/10.1145/3447993.3483240},
+ doi = {10.1145/3447993.3483240},
+ abstract = {Human gait is a widely used biometric trait for user identification and recognition. Given the wide-spreading, steady diffusion of ear-worn wearables (Earables) as the new frontier of wearable devices, we investigate the feasibility of earable-based gait identification. Specifically, we look at gait-based identification from the sounds induced by walking and propagated through the musculoskeletal system in the body. Our system, EarGate, leverages an in-ear facing microphone which exploits the earable's occlusion effect to reliably detect the user's gait from inside the ear canal, without impairing the general usage of earphones. With data collected from 31 subjects, we show that EarGate achieves up to 97.26\% Balanced Accuracy (BAC) with very low False Acceptance Rate (FAR) and False Rejection Rate (FRR) of 3.23\% and 2.25\%, respectively. Further, our measurement of power consumption and latency investigates how this gait identification model could live both as a stand-alone or cloud-coupled earable system.},
+ urldate = {2026-01-16},
+ booktitle = {Proceedings of the 27th {Annual} {International} {Conference} on {Mobile} {Computing} and {Networking}},
+ publisher = {Association for Computing Machinery},
+ author = {Ferlini, Andrea and Ma, Dong and Harle, Robert and Mascolo, Cecilia},
+ year = {2021},
+ pages = {337--349},
+ file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\K8K4QRXA\\Ferlini et al. - 2021 - EarGate gait-based user identification with in-ear microphones.pdf:application/pdf},
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@inproceedings{fan_headfi_2021,
+ address = {New York, NY, USA},
+ series = {{MobiCom} '21},
+ title = {{HeadFi}: bringing intelligence to all headphones},
+ isbn = {978-1-4503-8342-4},
+ shorttitle = {{HeadFi}},
+ url = {https://dl.acm.org/doi/10.1145/3447993.3448624},
+ doi = {10.1145/3447993.3448624},
+ abstract = {Headphones continue to become more intelligent as new functions (e.g., touch-based gesture control) appear. These functions usually rely on auxiliary sensors (e.g., accelerometer and gyroscope) that are available in smart headphones. However, for those headphones that do not have such sensors, supporting these functions becomes a daunting task. This paper presents HeadFi, a new design paradigm for bringing intelligence to headphones. Instead of adding auxiliary sensors into headphones, HeadFi turns the pair of drivers that are readily available inside all headphones into a versatile sensor to enable new applications spanning across mobile health, user-interface, and context-awareness. HeadFi works as a plug-in peripheral connecting the headphones and the pairing device (e.g., a smartphone). The simplicity (can be as simple as only two resistors) and small form factor of this design lend itself to be embedded into the pairing device as an integrated circuit. We envision HeadFi can serve as a vital supplementary solution to existing smart headphone design by directly transforming large amounts of existing "dumb" headphones into intelligent ones. We prototype HeadFi on PCB and conduct extensive experiments with 53 volunteers using 54 pairs of non-smart headphones under the institutional review board (IRB) protocols. The results show that HeadFi can achieve 97.2\%--99.5\% accuracy on user identification, 96.8\%--99.2\% accuracy on heart rate monitoring, and 97.7\%--99.3\% accuracy on gesture recognition.},
+ urldate = {2026-01-16},
+ booktitle = {Proceedings of the 27th {Annual} {International} {Conference} on {Mobile} {Computing} and {Networking}},
+ publisher = {Association for Computing Machinery},
+ author = {Fan, Xiaoran and Shangguan, Longfei and Rupavatharam, Siddharth and Zhang, Yanyong and Xiong, Jie and Ma, Yunfei and Howard, Richard},
+ year = {2021},
+ pages = {147--159},
+ file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\Z6UK4G74\\Fan et al. - 2021 - HeadFi bringing intelligence to all headphones.pdf:application/pdf},
+}
+</t>
+  </si>
+  <si>
+    <t>@article{ding_leakage_2022,
+ title = {Leakage or {Identification}: {Behavior}-irrelevant {User} {Identification} {Leveraging} {Leakage} {Current} on {Laptops}},
+ volume = {5},
+ shorttitle = {Leakage or {Identification}},
+ url = {https://dl.acm.org/doi/10.1145/3494984},
+ doi = {10.1145/3494984},
+ abstract = {The convenience of laptops brings with it the risk of information leakage, and conventional security systems based on the password or the explicit biometric do little to alleviate this problem. Biometric identification based on anatomical features provides far stronger security; however, a lack of suitable sensors on laptops limits the applicability of this technology. In this paper, we developed a behavior-irrelevant user identification system applicable to laptops with a metal casing. The proposed scheme, referred to as LeakPrint, is based on leakage current, wherein the system uses an earphone to capture current leaking through the body and then transmits the corresponding signal to a server for identification. The user identification is achieved via denoising, dimension reduction, and feature extraction. Compared to other biometric identification methods, the proposed system is less dependent on external hardware and more robust to environmental noise. The experiments in real-world environments demonstrated that LeakPrint can verify user identity with high accuracy (93.6\%), while providing effective defense against replay attacks (96.5\%) and mimicry attacks (90.9\%).},
+ number = {4},
+ urldate = {2026-01-16},
+ journal = {Proc. ACM Interact. Mob. Wearable Ubiquitous Technol.},
+ author = {Ding, Dian and Yang, Lanqing and Chen, Yi-Chao and Xue, Guangtao},
+ year = {2022},
+ pages = {152:1--152:23},
+ file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\K6HK9PR5\\Ding et al. - 2022 - Leakage or Identification Behavior-irrelevant User Identification Leveraging Leakage Current on Lap.pdf:application/pdf},
+}</t>
+  </si>
+  <si>
+    <t>@inproceedings{derawi_biometric_2016,
+ title = {Biometric acoustic ear recognition},
+ url = {https://ieeexplore.ieee.org/document/7835597},
+ doi = {10.1109/BIOSMART.2016.7835597},
+ abstract = {This paper deals with the holistic development of a biometric system based on acoustic ear recognition. Its main purpose is to map one aspects within acoustic ear recognition, namely the performance of the ear characteristics bands and peaks. 50 subjects have participated in experiments collecting biometric samples. The measuring device composed of a pair of headphones with an integrated microphone as sensor. Several methods have been utilized for feature extraction, and various types of distance metrics and classifiers have been employed.},
+ urldate = {2026-01-16},
+ booktitle = {2016 {International} {Conference} on {Bio}-engineering for {Smart} {Technologies} ({BioSMART})},
+ author = {Derawi, Mohammad},
+ month = dec,
+ year = {2016},
+ keywords = {Ear, Headphones, Microphones, Acoustics, Acoustic, Atmospheric measurements, Ear Recognition, Frequency measurement, Particle measurements},
+ pages = {1--4},
+ file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\CPG8SP97\\Derawi - 2016 - Biometric acoustic ear recognition.pdf:application/pdf},
+}</t>
+  </si>
+  <si>
+    <t>@inproceedings{curran_passthoughts_2016,
+ title = {Passthoughts authentication with low cost {EarEEG}},
+ issn = {1558-4615},
+ url = {https://ieeexplore.ieee.org/document/7591112},
+ doi = {10.1109/EMBC.2016.7591112},
+ abstract = {Personal and wearable computing are moving toward smaller and more seamless devices. We explore how this trend could be mirrored in an authentication scheme based on electroencephalography (EEG) signals collected from the ear. We evaluate this model using a low cost, single-channel, consumer grade device for data collection. Using data from 12 study participants who performed a set of 5 mental tasks, we achieve a 44\% reduction in half total error rate (HTER) compared with a random classifier, corresponding to a 72\% authentication accuracy in within-participants analyses and a 60\% reduction and 80\% accuracy in between-participant analyses. Given our results and those of previous research, we conclude that earEEG shows potential as a uniquely convenient authentication method as it is integrable into devices like earbud headphones already commonly worn in the ear, and the mental gestures generating the signal are invisible to would-be eavesdroppers.},
+ urldate = {2026-01-16},
+ booktitle = {2016 38th {Annual} {International} {Conference} of the {IEEE} {Engineering} in {Medicine} and {Biology} {Society} ({EMBC})},
+ author = {Curran, Max T. and Yang, Jong-kai and Merrill, Nick and Chuang, John},
+ month = aug,
+ year = {2016},
+ note = {ISSN: 1558-4615},
+ keywords = {Ear, Authentication, Electroencephalography, Sensors, Electrodes, Face, Testing},
+ pages = {1979--1982},
+ file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\MNK9IM44\\Curran et al. - 2016 - Passthoughts authentication with low cost EarEEG.pdf:application/pdf},
+}</t>
+  </si>
+  <si>
+    <t>@inproceedings{curran_one-step_2017,
+ address = {New York, NY, USA},
+ series = {{UbiComp} '17},
+ title = {One-step, three-factor authentication in a single earpiece},
+ isbn = {978-1-4503-5190-4},
+ url = {https://dl.acm.org/doi/10.1145/3123024.3123087},
+ doi = {10.1145/3123024.3123087},
+ abstract = {Multifactor authentication presents a robust security method, but typically requires multiple steps on the part of the user resulting in a high cost to usability and limiting adoption. Furthermore, a truly usable system must be unobtrusive and inconspicuous. Here, we present a system that provides all three factors of authentication (knowledge, possession, and inherence) in a single step in the form of an earpiece which implements brain-based authentication via custom-fit, in-ear electroencephalography (EEG). We demonstrate its potential by collecting EEG data using manufactured custom-fit earpieces with embedded electrodes. Across 7 participants, we are able to achieve perfect performance, mean 0\% false acceptance (FAR) and 0\% false rejection rates (FRR), using participants' best performing tasks collected in one session by one earpiece with three electrodes. Our results indicate that a single earpiece with embedded electrodes could provide a discreet, convenient, and robust method for secure one-step, three-factor authentication.},
+ urldate = {2026-01-16},
+ booktitle = {Proceedings of the 2017 {ACM} {International} {Joint} {Conference} on {Pervasive} and {Ubiquitous} {Computing} and {Proceedings} of the 2017 {ACM} {International} {Symposium} on {Wearable} {Computers}},
+ publisher = {Association for Computing Machinery},
+ author = {Curran, Max T. and Merrill, Nick and Chuang, John and Gandhi, Swapan},
+ year = {2017},
+ pages = {21--24},
+ file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\7FT9XIRU\\Curran et al. - 2017 - One-step, three-factor authentication in a single earpiece.pdf:application/pdf},
+}</t>
+  </si>
+  <si>
+    <t>@inproceedings{clarke_motion_2020,
+ address = {New York, NY, USA},
+ series = {{MUM} '20},
+ title = {Motion {Coupling} of {Earable} {Devices} in {Camera} {View}},
+ isbn = {978-1-4503-8870-2},
+ url = {https://dl.acm.org/doi/10.1145/3428361.3428470},
+ doi = {10.1145/3428361.3428470},
+ abstract = {Earables, earphones augmented with inertial sensors and real-time data accessibility, provide the opportunity for private audio channels in public settings. One of the main challenges of achieving this goal is to correctly associate which device belongs to which user without prior information. In this paper, we explore how motion of an earable, as measured by the on-board accelerometer, can be correlated against detected faces from a webcam to accurately match which user is wearing the device. We conduct a data collection and explore which type of user movement can be accurately detected using this approach, and investigate how varying the speed of the movement affects detection rates. Our results show that the approach achieves greater detection results for faster movements, and that it can differentiate the same movement across different participants with a detection rate of 86\%, increasing to 92\% when differentiating a movement against others.},
+ urldate = {2026-01-17},
+ booktitle = {Proceedings of the 19th {International} {Conference} on {Mobile} and {Ubiquitous} {Multimedia}},
+ publisher = {Association for Computing Machinery},
+ author = {Clarke, Christopher and Ehrich, Peter and Gellersen, Hans},
+ year = {2020},
+ pages = {13--17},
+ file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\LKE6Y3Y4\\Clarke et al. - 2020 - Motion Coupling of Earable Devices in Camera View.pdf:application/pdf},
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@inproceedings{arakawa_fast_2016,
+ title = {Fast and accurate personal authentication using ear acoustics},
+ url = {https://ieeexplore.ieee.org/document/7820886},
+ doi = {10.1109/APSIPA.2016.7820886},
+ abstract = {This paper presents a biometric personal-authentication method that exploits acoustic characteristics of human ears. It transmits a probe signal into the ear and receives its reflection, which contains personal identity information about the shape of the ear canal. Based on a study of effective and efficient acoustic feature representation and the use of audio equipment suitable for acquiring features with low within-individual variability, the proposed method achieves a promising equal error rate of 0.97\% with only 12 feature components. A prototype system for Android smartphones is also presented.},
+ urldate = {2026-01-16},
+ booktitle = {2016 {Asia}-{Pacific} {Signal} and {Information} {Processing} {Association} {Annual} {Summit} and {Conference} ({APSIPA})},
+ author = {Arakawa, Takayuki and Koshinaka, Takafumi and Yano, Shohei and Irisawa, Hideki and Miyahara, Ryoji and Imaoka, Hitoshi},
+ month = dec,
+ year = {2016},
+ keywords = {Ear, Irrigation, Authentication, Headphones, Smart phones, Mel frequency cepstral coefficient},
+ pages = {1--4},
+ file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\IC66LC5V\\Arakawa et al. - 2016 - Fast and accurate personal authentication using ear acoustics.pdf:application/pdf},
+}
+</t>
+  </si>
+  <si>
+    <t>@inproceedings{akkermans_acoustic_2005,
+ title = {Acoustic ear recognition for person identification},
+ url = {https://ieeexplore.ieee.org/document/1544428},
+ doi = {10.1109/AUTOID.2005.11},
+ abstract = {In this paper we investigate how the acoustic properties of the pinna-i.e., the outer flap of the ear- and the ear canal can be used as a biometric. The acoustic properties can be measured relatively easy with an inexpensive sensor and feature vectors can be derived with little effort. We achieve equal error rates in the order of 1.5\%-7\%, depending on the application device that is used to do the measurement.},
+ urldate = {2026-01-16},
+ booktitle = {Fourth {IEEE} {Workshop} on {Automatic} {Identification} {Advanced} {Technologies} ({AutoID}'05)},
+ author = {Akkermans, A.H.M. and Kevenaar, T.A.M. and Schobben, D.W.E.},
+ month = oct,
+ year = {2005},
+ keywords = {Ear, Irrigation, Acoustic devices, Acoustic measurements, Biometrics, Fingerprint recognition, Loudspeakers, Resonance, Shape, Transfer functions},
+ pages = {219--223},
+ file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\JFCZWR75\\Akkermans et al. - 2005 - Acoustic ear recognition for person identification.pdf:application/pdf},
 }</t>
   </si>
   <si>
@@ -1274,10 +1563,13 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1628,7 +1920,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B47"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1833,7 +2125,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B26" t="s">
         <v>26</v>
@@ -1841,7 +2133,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B27" t="s">
         <v>27</v>
@@ -1849,7 +2141,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B28" t="s">
         <v>28</v>
@@ -1857,7 +2149,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B29" t="s">
         <v>29</v>
@@ -1865,7 +2157,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B30" t="s">
         <v>30</v>
@@ -1873,10 +2165,138 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B31" t="s">
         <v>31</v>
+      </c>
+    </row>
+    <row r="32" ht="409.5" spans="1:2">
+      <c r="A32">
+        <v>33</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="33" ht="409.5" spans="1:2">
+      <c r="A33">
+        <v>34</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="34" ht="409.5" spans="1:2">
+      <c r="A34">
+        <v>35</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="35" ht="409.5" spans="1:2">
+      <c r="A35">
+        <v>36</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="36" ht="409.5" spans="1:2">
+      <c r="A36">
+        <v>37</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="37" ht="409.5" spans="1:2">
+      <c r="A37">
+        <v>38</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="38" ht="409.5" spans="1:2">
+      <c r="A38">
+        <v>39</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="39" ht="409.5" spans="1:2">
+      <c r="A39">
+        <v>40</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="40" ht="409.5" spans="1:2">
+      <c r="A40">
+        <v>41</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="41" ht="409.5" spans="1:2">
+      <c r="A41">
+        <v>42</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="42" ht="409.5" spans="1:2">
+      <c r="A42">
+        <v>43</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="43" ht="395.2" spans="1:2">
+      <c r="A43">
+        <v>44</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="44" ht="409.5" spans="1:2">
+      <c r="A44">
+        <v>45</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="45" ht="366.4" spans="1:2">
+      <c r="A45">
+        <v>46</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="46" ht="409.5" spans="1:2">
+      <c r="A46">
+        <v>47</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="47" ht="409.5" spans="1:2">
+      <c r="A47">
+        <v>48</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -1899,16 +2319,16 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -1916,19 +2336,19 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="C2">
         <v>0.425</v>
       </c>
       <c r="D2" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="E2" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="F2" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>

--- a/interconnections_datasets_auth/bibtex_mapping_of_ids_authentication.xlsx
+++ b/interconnections_datasets_auth/bibtex_mapping_of_ids_authentication.xlsx
@@ -36,603 +36,109 @@
     <t>Bibtex</t>
   </si>
   <si>
-    <t>@article{zou_earprint_2024,
-	title = {{EarPrint}: {Earphone}-{Based} {Implicit} {User} {Authentication} {With} {Behavioral} and {Physiological} {Acoustics}},
-	volume = {11},
-	issn = {2327-4662},
-	shorttitle = {{EarPrint}},
-	url = {https://ieeexplore.ieee.org/document/10566858},
-	doi = {10.1109/JIOT.2024.3417622},
-	abstract = {With the increasing pervasiveness of smart earphones, it is appealing to propose more unobtrusive and convenient wearable authentication methods. Researchers have designed earphone-based authentication systems which utilize high-frequency audio signals to scan ear canal structure. Nevertheless, they possess shortcomings of low unobtrusiveness and robustness. In this article, we put forward an earphone-based passive authentication system which makes use of physiological and behavioral acoustic signals caused by a user’s natural actions, including putting on earphones and inner organs’ activities, respectively. By introducing attention mechanism into the network design, our method adaptively weighs two channel signals, and extracts stable fingerprints for different people, which relieves model retraining for unseen users and improves its scalability. We have built a real-time prototype called EarPrint by designing the earphones and a mobile application, and conducted comprehensive experiments under diverse settings. Experimental results demonstrate that EarPrint has low false acceptance rate (FAR) and equal error rate (EER) less than 1\% and 5\% in most cases, respectively.},
-	number = {19},
-	urldate = {2025-11-27},
-	journal = {IEEE Internet of Things Journal},
-	author = {Zou, Yongpan and Weng, Jianhao and Lei, Haibo and Wang, Danyang and Leung, Victor C. M. and Wu, Kaishun},
-	month = oct,
-	year = {2024},
-	keywords = {Irrigation, Authentication, Headphones, user authentication, Deep learning, Sensors, Acoustics, Smart phones, Deep metric learning (DML), Identification of persons, Physiology, smart earphones},
-	pages = {31128--31143},
-	annote = {“earphone hardware and a self-developed mobile application” (Zou et al., 2024, p. 31131)
-“two stages of which one is during putting on earphones, and the other is when earphones are worn in ears” (Zou et al., 2024, p. 31132)
-“acoustic signals are mainly caused by the rubbing between an earpiece and the ear canal during putting-on activities” (Zou et al., 2024, p. 31132)
-“activities of viscera” (Zou et al., 2024, p. 31132)
-an attention mechanism-based learning network that extracts feature representations with assigning weights automatically” (Zou et al., 2024, p. 31132)
-“to authenticate the current user, we need to calculate the similarity between his/her feature vector and the stored feature vectors of legitimate users” (Zou et al., 2024, p. 31133)
-},
-	file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\6C6CP99J\\Zou et al. - 2024 - EarPrint Earphone-Based Implicit User Authentication With Behavioral and Physiological Acoustics.pdf:application/pdf},
-}</t>
-  </si>
-  <si>
-    <t>@article{zou_beyond_2023,
-	title = {Beyond {Legitimacy}, {Also} {With} {Identity}: {Your} {Smart} {Earphones} {Know} {Who} {You} {Are} {Quietly}},
-	volume = {22},
-	issn = {1558-0660},
-	shorttitle = {Beyond {Legitimacy}, {Also} {With} {Identity}},
-	url = {https://ieeexplore.ieee.org/document/9647983},
-	doi = {10.1109/TMC.2021.3134654},
-	abstract = {User authentication and identification on smart devices has great significance in keeping data privacy and recommending personalized services. With the rising popularity of smart earphones recently, they open up a new world for users to enjoy music individually, but also bring about privacy concerns at the same time. Existing few research works propose positive sensing systems that emit and receive inaudible acoustic signals to authenticate users. However, they share shortcomings of intrusiveness to users, high power consumption, and purely focusing on authentication. Instead, in this paper, we propose a passive sensing system called {\textbackslash}sf EarIDEarID with low-cost customized earphones which attains user authentication and identification at once. It makes use of a embedded microphone to sense body sounds spread out through ear canals and extract ‘fingerprints’ as a novel biometric feature. With self-designed earphones, we design a deep learning-based real-time data processing pipeline and cope with external interference. Extensive experiments under different real-world settings show that {\textbackslash}sf EarIDEarID can achieve a rather low false acceptance rate of 3.4\%3.4\% for user authentication and a high F1F1 score of 95.5\%95.5\% for legitimate user identification.},
-	number = {6},
-	urldate = {2025-11-27},
-	journal = {IEEE Transactions on Mobile Computing},
-	author = {Zou, Yongpan and Lei, Haibo and Wu, Kaishun},
-	month = jun,
-	year = {2023},
-	keywords = {Ear, Irrigation, Authentication, Headphones, Sensors, deep learning, earable device, Hardware, Microphones, User authentication},
-	pages = {3179--3192},
-	file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\XAM6SIXR\\Zou et al. - 2023 - Beyond Legitimacy, Also With Identity Your Smart Earphones Know Who You Are Quietly.pdf:application/pdf},
-}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@inproceedings{zhou_baroauth_2025,
- title = {{BaroAuth}: {Harnessing} {Ear} {Canal} {Deformation} for {Speaking} {User} {Authentication} on {Earbuds}},
- issn = {2575-8411},
- shorttitle = {{BaroAuth}},
- url = {https://ieeexplore.ieee.org/document/11183763},
- doi = {10.1109/ICDCS63083.2025.00020},
- abstract = {The growing adoption of smart wearable devices (e.g., earbuds and smart watches) poses new challenges for secure and seamless user authentication due to their limited interaction interfaces. Conventional biometric methods, including fingerprints, voice, and facial recognition, often suffer from usability constraints, noise interference, or susceptibility to spoofing attacks. In this paper, we propose BaroAuth, a novel authentication system that utilizes the stable and distinctive patterns of Speech-aware Pressure Sequences (SPSs) captured by miniature MEMS barometers embedded in earbuds. The design of BaroAuth is based on two key observations. First, speech production involves coordinated movements of articulatory organs, such as the jaw, tongue, and soft palate, which reshape the ear canal geometry via the temporomandibular joint (TMJ), generating subtle pressure variations that encode the speaker’s unique articulatory dynamics and physiological traits. Second, SPSs demonstrate strong intra-individual consistency and notable inter-individual variability, which can be effectively captured by barometers. We implement the prototype of BaroAuth and conduct comprehensive experiments on it. Experimental results demonstrate that BaroAuth achieves a mean false-acceptance rate (FAR) and false-rejection rate (FRR) of 1.62\% and 1.74\%, respectively, even under sophisticated attack scenarios.},
- urldate = {2025-11-28},
- booktitle = {2025 {IEEE} 45th {International} {Conference} on {Distributed} {Computing} {Systems} ({ICDCS})},
- author = {Zhou, Luo and Chang, Shan and Luo, Jiusong and Wen, Huixiang and Zhu, Hongzi and Lu, Li},
- month = jul,
- year = {2025},
- keywords = {Ear, Irrigation, Authentication, Feature extraction, Wearable devices, Physiology, barometer, Barometers, Deformation, ear canal deformation, earbuds, Microelectromechanical systems, speaking user authentication, Working environment noise},
- pages = {111--121},
- annote = {“pressure signals from the left and right ear canals precede audio signals recorded by a microphone” (Zhou et al., 2025, p. 113)
-},
- file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\H9B6X578\\Zhou et al. - 2025 - BaroAuth Harnessing Ear Canal Deformation for Speaking User Authentication on Earbuds.pdf:application/pdf},
+    <t>@inproceedings{akkermans_acoustic_2005,
+ title = {Acoustic ear recognition for person identification},
+ url = {https://ieeexplore.ieee.org/document/1544428},
+ doi = {10.1109/AUTOID.2005.11},
+ abstract = {In this paper we investigate how the acoustic properties of the pinna-i.e., the outer flap of the ear- and the ear canal can be used as a biometric. The acoustic properties can be measured relatively easy with an inexpensive sensor and feature vectors can be derived with little effort. We achieve equal error rates in the order of 1.5\%-7\%, depending on the application device that is used to do the measurement.},
+ urldate = {2026-01-16},
+ booktitle = {Fourth {IEEE} {Workshop} on {Automatic} {Identification} {Advanced} {Technologies} ({AutoID}'05)},
+ author = {Akkermans, A.H.M. and Kevenaar, T.A.M. and Schobben, D.W.E.},
+ month = oct,
+ year = {2005},
+ keywords = {Ear, Irrigation, Acoustic devices, Acoustic measurements, Biometrics, Fingerprint recognition, Loudspeakers, Resonance, Shape, Transfer functions},
+ pages = {219--223},
+ file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\JFCZWR75\\Akkermans et al. - 2005 - Acoustic ear recognition for person identification.pdf:application/pdf},
+}</t>
+  </si>
+  <si>
+    <t>@article{liu_earprint_2014,
+ title = {Earprint: {Transient} {Evoked} {Otoacoustic} {Emission} for {Biometrics}},
+ volume = {9},
+ issn = {1556-6021},
+ shorttitle = {Earprint},
+ url = {https://ieeexplore.ieee.org/document/6914592},
+ doi = {10.1109/TIFS.2014.2361205},
+ abstract = {Biometrics is attracting increasing attention in privacy and security concerned issues, such as access control and remote financial transaction. However, advanced forgery and spoofing techniques are threatening the reliability of conventional biometric modalities. This has been motivating our investigation of a novel yet promising modality transient evoked otoacoustic emission (TEOAE), which is an acoustic response generated from cochlea after a click stimulus. Unlike conventional modalities that are easily accessible or captured, TEOAE is naturally immune to replay and falsification attacks as a physiological outcome from human auditory system. In this paper, we resort to wavelet analysis to derive the time-frequency representation of such nonstationary signal, which reveals individual uniqueness and long-term reproducibility. A machine learning technique linear discriminant analysis is subsequently utilized to reduce intrasubject variability and further capture intersubject differentiation features. Considering practical application, we also introduce a complete framework of the biometric system in both verification and identification modes. Comparative experiments on a TEOAE data set of biometric setting show the merits of the proposed method. Performance is further improved with fusion of information from both ears.},
+ number = {12},
+ urldate = {2026-01-16},
+ journal = {IEEE Transactions on Information Forensics and Security},
+ author = {Liu, Yuxi and Hatzinakos, Dimitrios},
+ month = dec,
+ year = {2014},
+ keywords = {Feature extraction, Biometrics (access control), Auditory system, biometric fusion, linear discriminant analysis, Linear discriminant analysis, Robust biometric modality, Robust Biometric Modality, time-frequency analysis, Time-frequency analysis, Time-frequency Analysis, transient evoked otoacoustic emission, Transient Evoked Otoacoustic Emission},
+ pages = {2291--2301},
+ file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\ST468TL4\\Liu and Hatzinakos - 2014 - Earprint Transient Evoked Otoacoustic Emission for Biometrics.pdf:application/pdf},
+}</t>
+  </si>
+  <si>
+    <t>@inproceedings{derawi_biometric_2016,
+ title = {Biometric acoustic ear recognition},
+ url = {https://ieeexplore.ieee.org/document/7835597},
+ doi = {10.1109/BIOSMART.2016.7835597},
+ abstract = {This paper deals with the holistic development of a biometric system based on acoustic ear recognition. Its main purpose is to map one aspects within acoustic ear recognition, namely the performance of the ear characteristics bands and peaks. 50 subjects have participated in experiments collecting biometric samples. The measuring device composed of a pair of headphones with an integrated microphone as sensor. Several methods have been utilized for feature extraction, and various types of distance metrics and classifiers have been employed.},
+ urldate = {2026-01-16},
+ booktitle = {2016 {International} {Conference} on {Bio}-engineering for {Smart} {Technologies} ({BioSMART})},
+ author = {Derawi, Mohammad},
+ month = dec,
+ year = {2016},
+ keywords = {Ear, Headphones, Microphones, Acoustics, Acoustic, Atmospheric measurements, Ear Recognition, Frequency measurement, Particle measurements},
+ pages = {1--4},
+ file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\CPG8SP97\\Derawi - 2016 - Biometric acoustic ear recognition.pdf:application/pdf},
+}</t>
+  </si>
+  <si>
+    <t>@inproceedings{curran_passthoughts_2016,
+ title = {Passthoughts authentication with low cost {EarEEG}},
+ issn = {1558-4615},
+ url = {https://ieeexplore.ieee.org/document/7591112},
+ doi = {10.1109/EMBC.2016.7591112},
+ abstract = {Personal and wearable computing are moving toward smaller and more seamless devices. We explore how this trend could be mirrored in an authentication scheme based on electroencephalography (EEG) signals collected from the ear. We evaluate this model using a low cost, single-channel, consumer grade device for data collection. Using data from 12 study participants who performed a set of 5 mental tasks, we achieve a 44\% reduction in half total error rate (HTER) compared with a random classifier, corresponding to a 72\% authentication accuracy in within-participants analyses and a 60\% reduction and 80\% accuracy in between-participant analyses. Given our results and those of previous research, we conclude that earEEG shows potential as a uniquely convenient authentication method as it is integrable into devices like earbud headphones already commonly worn in the ear, and the mental gestures generating the signal are invisible to would-be eavesdroppers.},
+ urldate = {2026-01-16},
+ booktitle = {2016 38th {Annual} {International} {Conference} of the {IEEE} {Engineering} in {Medicine} and {Biology} {Society} ({EMBC})},
+ author = {Curran, Max T. and Yang, Jong-kai and Merrill, Nick and Chuang, John},
+ month = aug,
+ year = {2016},
+ note = {ISSN: 1558-4615},
+ keywords = {Ear, Authentication, Electroencephalography, Sensors, Electrodes, Face, Testing},
+ pages = {1979--1982},
+ file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\MNK9IM44\\Curran et al. - 2016 - Passthoughts authentication with low cost EarEEG.pdf:application/pdf},
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@inproceedings{arakawa_fast_2016,
+ title = {Fast and accurate personal authentication using ear acoustics},
+ url = {https://ieeexplore.ieee.org/document/7820886},
+ doi = {10.1109/APSIPA.2016.7820886},
+ abstract = {This paper presents a biometric personal-authentication method that exploits acoustic characteristics of human ears. It transmits a probe signal into the ear and receives its reflection, which contains personal identity information about the shape of the ear canal. Based on a study of effective and efficient acoustic feature representation and the use of audio equipment suitable for acquiring features with low within-individual variability, the proposed method achieves a promising equal error rate of 0.97\% with only 12 feature components. A prototype system for Android smartphones is also presented.},
+ urldate = {2026-01-16},
+ booktitle = {2016 {Asia}-{Pacific} {Signal} and {Information} {Processing} {Association} {Annual} {Summit} and {Conference} ({APSIPA})},
+ author = {Arakawa, Takayuki and Koshinaka, Takafumi and Yano, Shohei and Irisawa, Hideki and Miyahara, Ryoji and Imaoka, Hitoshi},
+ month = dec,
+ year = {2016},
+ keywords = {Ear, Irrigation, Authentication, Headphones, Smart phones, Mel frequency cepstral coefficient},
+ pages = {1--4},
+ file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\IC66LC5V\\Arakawa et al. - 2016 - Fast and accurate personal authentication using ear acoustics.pdf:application/pdf},
 }
 </t>
   </si>
   <si>
-    <t>@inproceedings{xie_earpass_2024,
-	title = {{EarPass}: {Unlock} {When} {Wearing} {Your} {Earphones}},
-	issn = {2575-8411},
-	shorttitle = {{EarPass}},
-	url = {https://ieeexplore.ieee.org/document/10631065},
-	doi = {10.1109/ICDCS60910.2024.00121},
-	abstract = {With the growing reliance on digital systems in today's mobile Internet era, robust authentication methods are crucial for safeguarding personal data and controlling access to resources. Conventional methods, such as knowledge-based and biometric-based authentication, are widely used but still have some usage limitations and potential security concerns, like wearing protective suits/masks or being imitated by attackers with ulterior motives. In this paper, we propose another earphone-based authentication system, namely EarPass, that leverages users' unique head motion patterns in response to a very short period of music segment. Here, we employ a Convolutional Neural Network (CNN)-based feature extractor to capture and map distinct head motions into a well-separated latent space, achieving high-dimensional data extraction. We demonstrate the consistency, uniqueness, and robustness of head motion patterns through extensive experiments and reach a 98.2\% F1-score, indicating superior performance compared to conventional authentication methods. Additionally, EarPass is user-friendly, secure, and adaptable to various environments, including noisy and movement-oriented scenarios. By integrating the authentication system into Android devices, we showcase its real-world applicability and low energy consumption with minimal latency. The source code of EarPass will be open-source to further research and collaboration within the community.},
-	urldate = {2025-11-27},
-	booktitle = {2024 {IEEE} 44th {International} {Conference} on {Distributed} {Computing} {Systems} ({ICDCS})},
-	author = {Xie, Yanze and Gao, Mengzhen and Liu, Xiaoning and Huana, Shuo and Cui, Helei and Yu, Zhiwen and Guo, Bin},
-	month = jul,
-	year = {2024},
-	keywords = {Authentication, Feature extraction, Headphones, user authentication, earphones, Energy consumption, head motion, Motion segmentation, System performance, ubiquitous computing, Ubiquitous computing},
-	pages = {1283--1293},
-	annote = {“users wear earphones while the system plays a random music segment. As the users perform head motions in response to the music, the terminal application initiates data collection. This process involves capturing two types of sensor data generated by the user: accelerometer data and gyroscope data” (Xie et al., 2024, p. 1286)
-},
-	file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\39FYYG69\\Xie et al. - 2024 - EarPass Unlock When Wearing Your Earphones.pdf:application/pdf},
-}</t>
-  </si>
-  <si>
-    <t>@article{xie_user_2024,
-	title = {User {Authentication} on {Earable} {Devices} via {Bone}-{Conducted} {Occlusion} {Sounds}},
-	volume = {21},
-	issn = {1941-0018},
-	url = {https://ieeexplore.ieee.org/document/10330729},
-	doi = {10.1109/TDSC.2023.3335368},
-	abstract = {With the rapid development of mobile devices and the fast increase of sensitive data, secure and convenient mobile authentication technologies are desired. Except for traditional passwords, many mobile devices have biometric-based authentication methods (e.g., fingerprint, voiceprint, and face recognition), but they are vulnerable to spoofing attacks. To solve this problem, we study new biometric features which are based on the dental occlusion and find that the bone-conducted sound of dental occlusion collected in binaural canals contains unique features of individual bones and teeth. Motivated by this, we propose a novel authentication system, TeethPass⁺+, which uses earbuds to collect occlusal sounds in binaural canals to achieve authentication. First, we design an event detection method based on spectrum variance to detect bone-conducted sounds. Then, we analyze the time-frequency domain of the sounds to filter out motion noises and extract unique features of users from four aspects: teeth structure, bone structure, occlusal location, and occlusal sound. Finally, we train a Triplet network to construct the user template, which is used to complete authentication. Through extensive experiments including 53 volunteers, the performance of TeethPass⁺+ in different environments is verified. TeethPass⁺+ achieves an accuracy of 98.6\% and resists 99.7\% of spoofing attacks.},
-	number = {4},
-	urldate = {2025-11-28},
-	journal = {IEEE Transactions on Dependable and Secure Computing},
-	author = {Xie, Yadong and Li, Fan and Wu, Yue and Wang, Yu},
-	month = jul,
-	year = {2024},
-	keywords = {Ear, Irrigation, Authentication, biometrics, Feature extraction, Biometrics (access control), acoustic sensing, Dentistry, Mobile authentication, occlusal sound, Teeth},
-	pages = {3704--3718},
-	annote = {“uses inward-facing microphones in earbuds to collect boneconducted sounds of dental occlusion in binaural canals to achieve authentication” (Xie et al., 2024, p. 3717)
-},
-	file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\23ZR7L7G\\Xie et al. - 2024 - User Authentication on Earable Devices via Bone-Conducted Occlusion Sounds.pdf:application/pdf},
-}</t>
-  </si>
-  <si>
-    <t>@inproceedings{wu_earae_2023,
-	title = {{EarAE}: {An} {Autoencoder} based {User} {Authentication} using {Earphones}},
-	issn = {2377-8644},
-	shorttitle = {{EarAE}},
-	url = {https://ieeexplore.ieee.org/document/10233591},
-	doi = {10.1109/ICCC57788.2023.10233591},
-	abstract = {Nowadays, earphone acts an increasingly vital role in human computer interaction. Throughout this trend, earphone-based user authentication, a new modality of biometric authentication, is winning more attention. Previous research leverage ear canal related features to authenticate users. These methods establish a binary classification model, based on the assumption that the identity information of all invalid users is given. However, they may not be effective when confronting new attackers.In this paper, we propose EarAE, a lightweight auto-encoder to address this problem. The basic idea is to model the authentication as a one-class classification problem, with features of the valid user as the single training class. Specifically, during training, the ear canal features of the valid user are fed into an autoencoder and reconstructed. EarAE learns to minimize the loss function between the input and the reconstructed counterparts. In this way, valid users will have a much lower loss function score than invalid users. Finally, a threshold is set to distinguish between valid/invalid users. Experimental results show that EarAE can achieve an averaged balanced accuracy of over 96\% across 30 subjects. This demonstrates a promising prospect of EarAE to serve as a reliable means of user authentication.},
-	urldate = {2025-11-27},
-	booktitle = {2023 {IEEE}/{CIC} {International} {Conference} on {Communications} in {China} ({ICCC})},
-	author = {Wu, Yuli and He, Jing},
-	month = aug,
-	year = {2023},
-	keywords = {Ear, Irrigation, Authentication, Training, Headphones, Computational modeling, Acoustic Sensing, Autoencoder, Ear Canal, Human computer interaction, User Authentication},
-	pages = {1--6},
-	annote = {“the sensing process lasts one second. The probe signal is designed as a 1kHz-21kHz chirp of 50 ms length that is emitted 5 times intermittently. Meanwhile, the inear microphone captures the reflected signals from ear canal” (Wu and He, 2023, p. 2)
-},
-	file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\U9GR8ZQU\\Wu and He - 2023 - EarAE An Autoencoder based User Authentication using Earphones.pdf:application/pdf},
-}</t>
-  </si>
-  <si>
-    <t>@article{wu_3d_2025,
-	title = {{3D} {Facial} {Tracking} and {User} {Authentication} {Through} {Lightweight} {Single}-{Ear} {Biosensors}},
-	volume = {24},
-	issn = {1558-0660},
-	url = {https://ieeexplore.ieee.org/abstract/document/10701549},
-	doi = {10.1109/TMC.2024.3470339},
-	abstract = {Facial landmark tracking and 3D reconstruction have gained considerable attention due to their numerous applications such as human-computer interactions, facial expression analysis, and emotion recognition, etc. Traditional approaches require users to be confined to a particular location and face a camera under constrained recording conditions, which prevents them from being deployed in many application scenarios involving human motions. In this paper, we propose the first single-earpiece lightweight biosensing system, BioFace-3D, that can unobtrusively, continuously, and reliably sense the entire facial movements, track 2D facial landmarks, and further render 3D facial animations. Our single-earpiece biosensing system takes advantage of the cross-modal transfer learning model to transfer the knowledge embodied in a high-grade visual facial landmark detection model to the low-grade biosignal domain. After training, our BioFace-3D can directly perform continuous 3D facial reconstruction from the biosignals, without any visual input. Additionally, by utilizing biosensors, we also showcase the potential for capturing both behavioral aspects, such as facial gestures, and distinctive individual physiological traits, establishing a comprehensive two-factor authentication/identification framework. Extensive experiments involving 16 participants demonstrate that BioFace-3D can accurately track 53 major facial landmarks with only 1.85 mm average error and 3.38\% normalized mean error, which is comparable with most state-of-the-art camera-based solutions. Experiments also show that the system can authenticate users with high accuracy (e.g., over 99.8\% within two trials for three gestures in series), low false positive rate (e.g., less 0.24\%), and is robust to various types of attacks.},
-	number = {2},
-	urldate = {2025-11-28},
-	journal = {IEEE Transactions on Mobile Computing},
-	author = {Wu, Yi and Zhang, Xiande and Wu, Tianhao and Zhou, Bing and Nguyen, Phuc and Liu, Jian},
-	month = feb,
-	year = {2025},
-	keywords = {Authentication, Training, user authentication, Sensors, Biological system modeling, Visualization, Mobile computing, 3D facial reconstruction, Biosensors, Facial animation, single-ear biosensing, Solid modeling, Three-dimensional displays, Tracking, wearable sensing},
-	pages = {749--762},
-	annote = {“BioFace-3D is the first single-earpiece biosensing system that can unobtrusively, continuously, and reliably sense the entire facial movements, track 2D facial landmarks, and further render 3D facial animations through fitting a 3D head model to the 2D facial landmarks.” (Wu et al., 2025, p. 750)
-},
-	file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\UVLHPV5B\\Wu et al. - 2025 - 3D Facial Tracking and User Authentication Through Lightweight Single-Ear Biosensors.pdf:application/pdf},
-}</t>
-  </si>
-  <si>
-    <t>@article{wang_earslide_2024,
-	title = {{EarSlide}: a {Secure} {Ear} {Wearables} {Biometric} {Authentication} {Based} on {Acoustic} {Fingerprint}},
-	volume = {8},
-	shorttitle = {{EarSlide}},
-	url = {https://dl.acm.org/doi/10.1145/3643515},
-	doi = {10.1145/3643515},
-	abstract = {Ear wearables (earables) are emerging platforms that are broadly adopted in various applications. There is an increasing demand for robust earables authentication because of the growing amount of sensitive information and the IoT devices that the earable could access. Traditional authentication methods become less feasible due to the limited input interface of earables. Nevertheless, the rich head-related sensing capabilities of earables can be exploited to capture human biometrics. In this paper, we propose EarSlide, an earable biometric authentication system utilizing the advanced sensing capacities of earables and the distinctive features of acoustic fingerprints when users slide their fingers on the face. It utilizes the inward-facing microphone of the earables and the face-ear channel of the ear canal to reliably capture the acoustic fingerprint. In particular, we study the theory of friction sound and categorize the characteristics of the acoustic fingerprints into three representative classes, pattern-class, ridge-groove-class, and coupling-class. Different from traditional fingerprint authentication only utilizes 2D patterns, we incorporate the 3D information in acoustic fingerprint and indirectly sense the fingerprint for authentication. We then design representative sliding gestures that carry rich information about the acoustic fingerprint while being easy to perform. It then extracts multi-class acoustic fingerprint features to reflect the inherent acoustic fingerprint characteristic for authentication. We also adopt an adaptable authentication model and a user behavior mitigation strategy to effectively authenticate legit users from adversaries. The key advantages of EarSlide are that it is resistant to spoofing attacks and its wide acceptability. Our evaluation of EarSlide in diverse real-world environments with intervals over one year shows that EarSlide achieves an average balanced accuracy rate of 98.37\% with only one sliding gesture.},
-	number = {1},
-	urldate = {2025-11-26},
-	journal = {Proc. ACM Interact. Mob. Wearable Ubiquitous Technol.},
-	author = {Wang, Zi and Wang, Yilin and Yang, Jie},
-	year = {2024},
-	pages = {24:1--24:29},
-	annote = {“We capture representive features from pattern-class, ridge-groove-class, and coupling-class to extract 2D patterns, 3D ridgegroove, and coupling information of finger-face sliding interaction. We adopt of a Siamese neural network for adaptable authentication model and a strategy for user behavior mitigation to enhance our system’s performance.” (Wang et al., 2024, p. 27)
-},
-	file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\TRUM5CIM\\Wang et al. - 2024 - EarSlide a Secure Ear Wearables Biometric Authentication Based on Acoustic Fingerprint.pdf:application/pdf},
-}</t>
-  </si>
-  <si>
-    <t>@article{wang_toothsonic_2022,
-	title = {{ToothSonic}: {Earable} {Authentication} via {Acoustic} {Toothprint}},
-	volume = {6},
-	shorttitle = {{ToothSonic}},
-	url = {https://dl.acm.org/doi/10.1145/3534606},
-	doi = {10.1145/3534606},
-	abstract = {Earables (ear wearables) are rapidly emerging as a new platform encompassing a diverse range of personal applications. The traditional authentication methods hence become less applicable and inconvenient for earables due to their limited input interface. Nevertheless, earables often feature rich around-the-head sensing capability that can be leveraged to capture new types of biometrics. In this work, we propose ToothSonic that leverages the toothprint-induced sonic effect produced by a user performing teeth gestures for earable authentication. In particular, we design representative teeth gestures that can produce effective sonic waves carrying the information of the toothprint. To reliably capture the acoustic toothprint, it leverages the occlusion effect of the ear canal and the inward-facing microphone of the earables. It then extracts multi-level acoustic features to reflect the intrinsic toothprint information for authentication. The key advantages of ToothSonic are that it is suitable for earables and is resistant to various spoofing attacks as the acoustic toothprint is captured via the user's private teeth-ear channel that modulates and encrypts the sonic waves. Our experiment studies with 25 participants show that ToothSonic achieves up to 95\% accuracy with only one of the users' tooth gestures.},
-	number = {2},
-	urldate = {2025-11-26},
-	journal = {Proc. ACM Interact. Mob. Wearable Ubiquitous Technol.},
-	author = {Wang, Zi and Ren, Yili and Chen, Yingying and Yang, Jie},
-	year = {2022},
-	pages = {78:1--78:24},
-	annote = {“a secure earable authentication system that leverages the toothprint-induced sonic waves for user authentication” (Wang et al., 2022, p. 20)
-},
-	file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\H7ZTB3YV\\Wang et al. - 2022 - ToothSonic Earable Authentication via Acoustic Toothprint.pdf:application/pdf},
-}</t>
-  </si>
-  <si>
-    <t>@article{wang_budsauth_2024,
-	title = {{BudsAuth}: {Toward} {Gesture}-{Wise} {Continuous} {User} {Authentication} {Through} {Earbuds} {Vibration} {Sensing}},
-	volume = {11},
-	issn = {2327-4662},
-	shorttitle = {{BudsAuth}},
-	url = {https://ieeexplore.ieee.org/document/10478100},
-	doi = {10.1109/JIOT.2024.3380811},
-	abstract = {The surge in popularity of wireless headphones, particularly wireless earbuds, as smart wearables, has been notable in recent years. These devices, empowered by artificial intelligence (AI), are broadening their utility in areas such as speech recognition, augmented reality, pose recognition, and health care monitoring, thereby enriching user experiences through novel interactive interfaces driven by embedded sensors. However, the widespread adoption of wireless earbuds has spurred concerns regarding security and privacy, necessitating robust bespoke security measures. Despite the miniaturization of mobile chips enabling the integration of sophisticated algorithms into smart wearables, the research and industrial communities have yet to accord adequate attention to earbud security. This article focuses on empowering wireless earbuds to authenticate their legitimate users, tackling the challenges associated with conventional authentication methods. Instead of relying on input interface authentication methods like PIN or lock patterns, this research delves into leveraging inertial measurement unit (IMU) data collected during interactions with devices to extract novel biometric features, presenting an alternative approach that nonetheless confronts challenges related to signal capture and interference. Consequently, we propose and design BudsAuth, an implicit user authentication framework that harnesses built-in IMU sensors in smart earbuds to capture vibration signals induced by on-face touching interactions with the earbuds. These vibrations are utilized to deliver continuous and implicit user authentication with high precision and compatibility across various earbud models. Extensive evaluation demonstrates BudsAuth’s capability to achieve an equal error rate (EER) of 0.0003, representing an approximate 99.97\% accuracy with seven consecutive samples of interactive gestures for implicit authentication.},
-	number = {12},
-	urldate = {2025-11-27},
-	journal = {IEEE Internet of Things Journal},
-	author = {Wang, Yong and Yang, Tianyu and Wang, Chunxiao and Li, Feng and Hu, Pengfei and Shen, Yiran},
-	month = jun,
-	year = {2024},
-	keywords = {Authentication, Sensors, Wearable devices, Adversarial learning, Communication system security, implicit authentication, Security, wearable computing, Wireless communication, Wireless sensor networks},
-	pages = {22007--22020},
-	annote = {“In the authentication phase, BudsAuth receives new vibration signals generated by an on-skin gesture. It extracts features using the personalized feature encoder obtained from the registration phase. BudsAuth performs implicit user authentication and spoofer detection by comparing the extracted features with the templates of the registered user. Finally, a weighted voting method is adopted to fuse the results from multiple consecutive on-skin gestures to achieve highprecision implicit authentication.” (Wang et al., 2024, p. 22010)
-},
-	file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\RW99TCPR\\Wang et al. - 2024 - BudsAuth Toward Gesture-Wise Continuous User Authentication Through Earbuds Vibration Sensing.pdf:application/pdf},
-}</t>
-  </si>
-  <si>
-    <t>@article{sun_earmonitor_2023,
-	title = {Earmonitor: {In}-ear {Motion}-resilient {Acoustic} {Sensing} {Using} {Commodity} {Earphones}},
-	volume = {6},
-	shorttitle = {Earmonitor},
-	url = {https://dl.acm.org/doi/10.1145/3569472},
-	doi = {10.1145/3569472},
-	abstract = {Earphones are emerging as the most popular wearable devices and there has been a growing trend in bringing intelligence to earphones. Previous efforts include adding extra sensors (e.g., accelerometer and gyroscope) or peripheral hardware to make earphones smart. These methods are usually complex in design and also incur additional cost. In this paper, we present Earmonitor, a low-cost system that uses the in-ear earphones to achieve sensing purposes. The basic idea behind Earmonitor is that each person's ear canal varies in size and shape. We therefore can extract the unique features from the ear canal-reflected signals to depict the personalized differences in ear canal geometry. Furthermore, we discover that the signal variations are also affected by the fine-grained physiological activities. We can therefore further detect the subtle heartbeat from the ear canal reflections. Experiments show that Earmonitor can achieve up to 96.4\% Balanced Accuracy (BAC) and low False Acceptance Rate (FAR) for user identification on a large-scale data of 120 subjects. For heartbeat monitoring, without any training, we propose signal processing schemes to achieve high sensing accuracy even in the most challenging scenarios when the target is walking or running.},
-	number = {4},
-	urldate = {2025-11-26},
-	journal = {Proc. ACM Interact. Mob. Wearable Ubiquitous Technol.},
-	author = {Sun, Xue and Xiong, Jie and Feng, Chao and Deng, Wenwen and Wei, Xudong and Fang, Dingyi and Chen, Xiaojiang},
-	year = {2023},
-	pages = {182:1--182:22},
-	annote = {“we propose Earmonitor hosted on low-cost earphones by simply adding a cheap in-ear microphone to achieve fine-grained sensing including user identification and heartbeat monitoring” (Sun et al., 2023, p. 20)
-},
-	file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\DQD5ICIK\\Sun et al. - 2023 - Earmonitor In-ear Motion-resilient Acoustic Sensing Using Commodity Earphones.pdf:application/pdf},
-}</t>
-  </si>
-  <si>
-    <t>@inproceedings{srivastava_jawthenticate_2024,
-	address = {New York, NY, USA},
-	series = {{SenSys} '23},
-	title = {Jawthenticate: {Microphone}-free {Speech}-based {Authentication} using {Jaw} {Motion} and {Facial} {Vibrations}},
-	isbn = {979-8-4007-0414-7},
-	shorttitle = {Jawthenticate},
-	url = {https://dl.acm.org/doi/10.1145/3625687.3625813},
-	doi = {10.1145/3625687.3625813},
-	abstract = {In this paper, we present Jawthenticate, an earable system that authenticates a user using audible or inaudible speech without using a microphone. This system can overcome the shortcomings of traditional voice-based authentication systems like unreliability in noisy conditions and spoofing using microphone-based replay attacks. Jawthenticate derives distinctive speech-related features from the jaw motion and associated facial vibrations. This combination of features makes Jawthenticate resilient to vocal imitations as well as camera-based spoofing. We use these features to train a two-class SVM classifier for each user. Our system is invariant to the content and language of speech. In a study conducted with 41 subjects, who speak different native languages, Jawthenticate achieves a Balanced Accuracy (BAC) of 97.07\%, True Positive Rate (TPR) of 97.75\%, and True Negative Rate (TNR) of 96.4\% with just 3 seconds of speech data.},
-	urldate = {2025-11-26},
-	booktitle = {Proceedings of the 21st {ACM} {Conference} on {Embedded} {Networked} {Sensor} {Systems}},
-	publisher = {Association for Computing Machinery},
-	author = {Srivastava, Tanmay and Pan, Shijia and Nguyen, Phuc and Jain, Shubham},
-	year = {2024},
-	pages = {209--222},
-	file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\U35K293W\\Srivastava et al. - 2024 - Jawthenticate Microphone-free Speech-based Authentication using Jaw Motion and Facial Vibrations.pdf:application/pdf},
-}</t>
-  </si>
-  <si>
-    <t>@inproceedings{mizuho_earauthcam_2024,
-	address = {New York, NY, USA},
-	series = {{AHs} '24},
-	title = {{EarAuthCam}: {Personal} {Identification} and {Authentication} {Method} {Using} {Ear} {Images} {Acquired} with a {Camera}-{Equipped} {Hearable} {Device}},
-	isbn = {979-8-4007-0980-7},
-	shorttitle = {{EarAuthCam}},
-	url = {https://dl.acm.org/doi/10.1145/3652920.3653059},
-	doi = {10.1145/3652920.3653059},
-	abstract = {Earphones are now used for longer hours than before with the advancement in wireless technology and miniaturization. In addition, the application of earphones has become more diverse, and opportunities to access highly confidential information through them have increased. We propose a method comprising a hearable device equipped with a small camera for user authentication from ear images. This method improves the security of the hearable device. Ear images are first captured with the camera. The ear regions in the images are then extracted using a mask region-based convolutional neural network. Finally, the user is identified using histograms of oriented gradient features and a support vector machine (SVM). Our method was able to identify 18 participants with an accuracy of 84.1\%. Users are authenticated through unsupervised anomaly detection using an autoencoder with an error rate of 8.36\%. This method facilitates hands- and eye-free operations without requiring any explicit authentication action by the user.},
-	urldate = {2025-11-26},
-	booktitle = {Proceedings of the {Augmented} {Humans} {International} {Conference} 2024},
-	publisher = {Association for Computing Machinery},
-	author = {Mizuho, Yurina and Kawasaki, Yohei and Amesaka, Takashi and Sugiura, Yuta},
-	year = {2024},
-	pages = {119--130},
-	file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\TC7SFSQA\\Mizuho et al. - 2024 - EarAuthCam Personal Identification and Authentication Method Using Ear Images Acquired with a Camer.pdf:application/pdf},
-}</t>
-  </si>
-  <si>
-    <t>@article{liu_secure_2023,
-	title = {Secure {User} {Verification} and {Continuous} {Authentication} via {Earphone} {IMU}},
-	volume = {22},
-	issn = {1558-0660},
-	url = {https://ieeexplore.ieee.org/abstract/document/9841001},
-	doi = {10.1109/TMC.2022.3193847},
-	abstract = {Biometric plays an important role in user authentication. However, the most widely used biometrics, such as facial feature and fingerprint, are easy to capture or record, and thus vulnerable to spoofing attacks. On the contrary, intracorporal biometrics, such as electrocardiography and electroencephalography, are hard to collect, and hence more secure for authentication. Unfortunately, adopting them is not user-friendly due to their complicated collection methods or inconvenient constraints on users. In this paper, we propose a novel biometric-based authentication system, namely MandiPass. MandiPass leverages inertial measurement units, which have been widely deployed in portable devices, to collect intracorporal biometric from the vibration of user's mandible. It provides not only one-time verification function but also continuous authentication function. Both the two functions are secure and user-friendly. We theoretically validate the feasibility of MandiPass and develop a series of deep learning techniques for effective biometric extraction. We also utilize a Gaussian matrix to defend against replay attacks. Extensive experiment results with 34 volunteers show that MandiPass can achieve low equal error rate, even under various harsh environments.},
-	number = {11},
-	urldate = {2025-11-27},
-	journal = {IEEE Transactions on Mobile Computing},
-	author = {Liu, Jianwei and Song, Wenfan and Shen, Leming and Han, Jinsong and Ren, Kui},
-	month = nov,
-	year = {2023},
-	keywords = {Ear, Authentication, biometrics, Headphones, Biological system modeling, Biometrics (access control), continuous authentication, inertial measurement units, Standards, User verification, Vibrations},
-	pages = {6755--6769},
-	file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\LPJJYPJA\\Liu et al. - 2023 - Secure User Verification and Continuous Authentication via Earphone IMU.pdf:application/pdf},
-}</t>
-  </si>
-  <si>
-    <t>@article{liu_decoding_2025,
-	title = {Decoding {Air} {Friction} {Rhythms}: {Enabling} {User} {Identification} with {Out}-{Ear} {Microphones} in {COTS} {Earphones}},
-	issn = {1558-0660},
-	shorttitle = {Decoding {Air} {Friction} {Rhythms}},
-	url = {https://ieeexplore.ieee.org/document/11219195},
-	doi = {10.1109/TMC.2025.3626359},
-	abstract = {Ear-worn devices (earables) are increasingly central to smart system interactions involving privacy-sensitive data, yet secure user authentication on these devices remains a challenge. Existing methods often depend on auxiliary sensors like in-ear microphones or accelerometers, which are absent in many commercial earables. This paper introduces a novel biometric approach leveraging natural head gestures. We observe that head gestures generate unique air friction patterns detectable by out-ear microphones, producing sonic signatures shaped by the head and neck's musculoskeletal dynamics. These signatures serve as a robust basis for earable authentication. We propose HMPrint, a system that captures air-friction-induced sonic effects (AFiSe) from head gestures via outear microphones for authentication. HMPrint incorporates advanced spectral analysis, synthetic data generation using variational autoencoders, and a contrastive continual learning framework to enhance robustness against inconsistent wearing postures, varied movement patterns, and environmental noise. A proof-of-concept prototype was tested with 30 participants and 15 commercial earable models across diverse conditions. Results show that HMPrint achieves high authentication accuracy (97.49\% recall), a low FAR (2.34\%), and strong resistance to spoofing (98\% success rate).},
-	urldate = {2025-11-28},
-	journal = {IEEE Transactions on Mobile Computing},
-	author = {Liu, Daibo and Lu, Hang and Qi, Xiaomeng and Rong, Huigui and Chen, Haowen and Jiang, Hongbo},
-	year = {2025},
-	keywords = {Ear, Authentication, Biometrics, Transfer functions, Headphones, user authentication, Sensors, Microphones, Acoustics, Microelectromechanical systems, Mobile computing, earables, head gestures, Neck, out-ear micophones},
-	pages = {1--16},
-	file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\LSS2EJQV\\Liu et al. - 2025 - Decoding Air Friction Rhythms Enabling User Identification with Out-Ear Microphones in COTS Earphon.pdf:application/pdf},
-}</t>
-  </si>
-  <si>
-    <t>@inproceedings{li_earpass_2023,
-	address = {New York, NY, USA},
-	series = {{UbiComp}/{ISWC} '23 {Adjunct}},
-	title = {{EarPass}: {Continuous} {User} {Authentication} with {In}-ear {PPG}},
-	isbn = {979-8-4007-0200-6},
-	shorttitle = {{EarPass}},
-	url = {https://dl.acm.org/doi/10.1145/3594739.3610670},
-	doi = {10.1145/3594739.3610670},
-	abstract = {In the rapidly expanding universe of smart IoT, earable devices, such as smart headphones and hearing aids, are gaining remarkable popularity. As we anticipate a future where a myriad of sophisticated applications—interaction, communication, health monitoring, and fitness guidance—migrate to earable devices handling sensitive and private information, the need for a robust, continuous authentication system for these devices becomes more critical than ever. Yet, current earable-based solutions, which rely predominantly on audio signals, are marred by inherent drawbacks such as privacy concerns, high costs, and noise interference. In light of these challenges, we investigate the potential of leveraging photoplethysmogram (PPG) sensors, which monitor key cardiac activities and reflect the uniqueness of an individual’s cardiac system, for earable authentication. Our study presents EarPass, an innovative ear-worn system that introduces a novel pipeline for the extraction and classification of in-ear PPG features to enable continuous user authentication. Initially, we preprocess the input in-ear PPG signals to facilitate this feature extraction and classification. Additionally, we present a method for detecting and eliminating motion artifacts (MAs) caused by head motions. Through extensive experiments, we not only demonstrate the effectiveness of our proposed design, but also establish the feasibility of using in-ear PPG for continuous user authentication—a significant stride towards more secure and efficient earable technologies.},
-	urldate = {2025-11-26},
-	booktitle = {Adjunct {Proceedings} of the 2023 {ACM} {International} {Joint} {Conference} on {Pervasive} and {Ubiquitous} {Computing} \&amp; the 2023 {ACM} {International} {Symposium} on {Wearable} {Computing}},
-	publisher = {Association for Computing Machinery},
-	author = {Li, Jiao and Liu, Yang and Li, Zhenjiang and Zhang, Jin},
-	year = {2023},
-	pages = {327--332},
-	file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\IT5YXTLN\\Li et al. - 2023 - EarPass Continuous User Authentication with In-ear PPG.pdf:application/pdf},
-}</t>
-  </si>
-  <si>
-    <t>@inproceedings{li_piezobud_2024,
-	address = {New York, NY, USA},
-	series = {{SenSys} '24},
-	title = {{PiezoBud}: {A} {Piezo}-{Aided} {Secure} {Earbud} with {Practical} {Speaker} {Authentication}},
-	isbn = {979-8-4007-0697-4},
-	shorttitle = {{PiezoBud}},
-	url = {https://dl.acm.org/doi/10.1145/3666025.3699358},
-	doi = {10.1145/3666025.3699358},
-	abstract = {With the advancement of AI-powered personal voice assistants, speaker authentication via earbuds has become increasingly vital, serving as a critical interface between users and mobile devices. However, existing audio-based speaker authentication methods fail to defend against voice spoofing threats such as replay and deep-fake attacks. To counteract these risks, we introduce PiezoBud, a pioneering multi-modal user authentication system that is truly practical and lightweight for earbuds. PiezoBud uses miniature piezoelectric sensors to detect micro-vibrations on the skin, extracting user-specific biometric data to authenticate legitimate access on the local smartphone and protect against malicious attacks. Our exploratory study, involving 85 participants, demonstrates the effectiveness of PiezoBud in various everyday scenarios, including ambient noise, body movement, and in-ear media playing. Using only 15 seconds of enrollment data, PiezoBud achieves an Equal Error Rate (EER) of 1.05\% and attain a mean authentication latency of 0.06 seconds on mobile devices. We also evaluate PiezoBud's effectiveness in countering challenging adaptive attack scenarios and its overall performance in various real-world situations. Our evaluation highlights that PiezoBud stands out as a practical, resilient, responsive, and secure option for earbuds users.},
-	urldate = {2025-11-27},
-	booktitle = {Proceedings of the 22nd {ACM} {Conference} on {Embedded} {Networked} {Sensor} {Systems}},
-	publisher = {Association for Computing Machinery},
-	author = {Li, Gen and Zeng, Huaili and Guo, Hanqing and Ren, Yidong and Dixon, Aiden and Cao, Zhichao and Li, Tianxing},
-	year = {2024},
-	pages = {564--577},
-	file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\VLIS498C\\Li et al. - 2024 - PiezoBud A Piezo-Aided Secure Earbud with Practical Speaker Authentication.pdf:application/pdf},
-}</t>
-  </si>
-  <si>
-    <t>@inproceedings{kawasaki_identification_2023,
-	title = {Identification and {Authentication} using {Clavicles}},
-	url = {https://ieeexplore.ieee.org/document/10354211/similar},
-	doi = {10.23919/SICE59929.2023.10354211},
-	abstract = {In recent years, wireless devices have become smaller and more portable. In addition, it is thought that personal identification and authentication will be necessary when they are used as independent terminals similar to smartphones. In this study, we focus on a neck-mounted earphone and propose personal identification and authentication using the acoustic characteristics of the clavicle, taking advantage of the fact that the clavicle touches the device when it is worn. Active acoustic sensing was used to measure the acoustic characteristics of the clavicle and extract its acoustic features. The accuracy was 98.8\%, and the EER was 4.0\% in five persons.},
-	urldate = {2025-11-27},
-	booktitle = {2023 62nd {Annual} {Conference} of the {Society} of {Instrument} and {Control} {Engineers} ({SICE})},
-	author = {Kawasaki, Yohei and Sugiura, Yuta},
-	month = sep,
-	year = {2023},
-	keywords = {Authentication, Feature extraction, Acoustic measurements, Wireless communication, Wireless sensor networks, Acoustics, Active acoustic sensing, authentication, identification, White noise},
-	pages = {1141--1145},
-	file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\89ILX8G8\\Kawasaki and Sugiura - 2023 - Identification and Authentication using Clavicles.pdf:application/pdf},
-}</t>
-  </si>
-  <si>
-    <t>@article{huang_eve_2025,
-	title = {Eve {Said} {Yes}: {AirBone} {Authentication} for {Head}-{Wearable} {Smart} {Voice} {Assistant}},
-	volume = {24},
-	issn = {1558-0660},
-	shorttitle = {Eve {Said} {Yes}},
-	url = {https://ieeexplore.ieee.org/document/10947223},
-	doi = {10.1109/TMC.2025.3530962},
-	abstract = {Recent advances in speech and language processing have led to the rise of smart voice services like Alexa, Google Home, and Siri. However, these advancements also increase security risks due to sophisticated voice domain attacks. Instead of relying on acoustic clues to detect replayed or synthesized speech, we utilize microphones and motion sensors in head-wearable devices to authorize legitimate users through bone-conducted vibrations, enabling multi-factor authentication (MFA) for spoken voice. Our proposed two-stage authentication system, AirBone, captures air and bone conduction (AirBone) signals and exploits two authentication factors sequentially. The first stage, called temporal consistency scoring (TCS), employs signal processing to verify the recorded AC and BC signals are concurrent and originate from the same vocalization process. Statistical tools are employed to distinguish legitimate attempts against false-triggering or acoustic attacks. The second stage leverages deep learning to verify the user’s unique bone conduction patterns in the vibration domain. Specifically, we enhance the robustness through data augmentation with constant-Q transform and adversarial training, improving the model’s ability to detect impersonation and machine-induced vibrations. Thanks to these designs, AirBone authentication offers enhanced security via MFA with no extra cost of user effort. In addition, our experimental results demonstrate a 96.3\%96.3\% overall accuracy, robustness against AirBone noise and room impulse responses, and 0.3\%0.3\% Equal Error Rate (EER) against acoustic and cross-domain attacks.},
-	number = {9},
-	urldate = {2025-11-28},
-	journal = {IEEE Transactions on Mobile Computing},
-	author = {Huang, Chenpei and Zhong, Hui and Prakash, Pavana and Shi, Dian and Yuan, Xu and Pan, Miao},
-	month = sep,
-	year = {2025},
-	keywords = {Ear, Authentication, Training, Vibrations, Security, User authentication, Acoustics, Bones, metaverse, Motion detection, multi-factor authentication, security and privacy, Solids, Spectrogram},
-	pages = {7836--7850},
-	file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\M8LGLQ2E\\Huang et al. - 2025 - Eve Said Yes AirBone Authentication for Head-Wearable Smart Voice Assistant.pdf:application/pdf},
-}</t>
-  </si>
-  <si>
-    <t>@inproceedings{hu_lightweight_2023,
-	address = {New York, NY, USA},
-	series = {{HotMobile} '23},
-	title = {Lightweight and {Non}-{Invasive} {User} {Authentication} on {Earables}},
-	isbn = {979-8-4007-0017-0},
-	url = {https://dl.acm.org/doi/10.1145/3572864.3580332},
-	doi = {10.1145/3572864.3580332},
-	abstract = {The widespread adoption of wireless earbuds has advanced the developments in earable-based sensing in various domains like entertainment, human-computer interaction, and health monitoring. Recently, researchers have shown an increased interest in user authentication using earables. Despite the successes witnessed in acoustic probing and speech based authentication systems, this paper proposed a lightweight and non-invasive ambient sound based user authentication scheme. It employs the difference between the in-ear and out-ear sounds to estimate the individual-specific occluded ear canal transfer function (OECTF). Specifically, the \{out-ear, in-ear\} scaling factors at different frequency bands are captured via linear regression and treated as the OECTF for user authentication. The proposed system is validated using 12 subjects under six different noisy environments and achieves a Balanced Error Rate (BER) of 4.84\%. The particularly lightweight system can be easily deployed in earbuds and paves the pathway for more personalized services.},
-	urldate = {2025-11-26},
-	booktitle = {Proceedings of the 24th {International} {Workshop} on {Mobile} {Computing} {Systems} and {Applications}},
-	publisher = {Association for Computing Machinery},
-	author = {Hu, Changshuo and Ma, Xiao and Ma, Dong and Dang, Ting},
-	year = {2023},
-	pages = {36--41},
-	file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\IIFYH39D\\Hu et al. - 2023 - Lightweight and Non-Invasive User Authentication on Earables.pdf:application/pdf},
-}</t>
-  </si>
-  <si>
-    <t>@article{hu_lr-auth_2024,
-	title = {{LR}-{Auth}: {Towards} {Practical} {Implementation} of {Implicit} {User} {Authentication} on {Earbuds}},
-	volume = {8},
-	shorttitle = {{LR}-{Auth}},
-	url = {https://dl.acm.org/doi/10.1145/3699793},
-	doi = {10.1145/3699793},
-	abstract = {The increasing use of earbuds in applications like immersive entertainment and health monitoring necessitates effective implicit user authentication systems to preserve the privacy of sensitive data and provide personalized experiences. Existing approaches, which leverage physiological cues (e.g., jawbone structure) and behavioral cues (e.g., gait), face challenges such as limited usability, high delay and energy overhead, and significant computational demands, rendering them impractical for resource-constrained earbuds. To address these issues, we present LR-Auth, a lightweight, user-friendly implicit authentication system designed for various earbud usage scenarios. LR-Auth utilizes the modulation of sound frequencies by the user's unique occluded ear canal, generating user-specific templates through linear correlations between two audio streams instead of complex machine-learning models. Our prototype, evaluated with 30 subjects under diverse conditions, demonstrates over 99\% balanced accuracy with five 100 ms audio segments, even in noisy environments and during music playback. LR-Auth significantly reduces system overhead, achieving a 20 × to 404 × decrease in latency and a 24 × to 410 × decrease in energy consumption compared to existing methods. These results highlight LR-Auth's potential for accurate, robust, and efficient user authentication on resource-constrained earbuds.},
-	number = {4},
-	urldate = {2025-11-27},
-	journal = {Proc. ACM Interact. Mob. Wearable Ubiquitous Technol.},
-	author = {Hu, Changshuo and Ma, Xiao and Huang, Xinger and Shen, Yiran and Ma, Dong},
-	year = {2024},
-	pages = {155:1--155:27},
-	file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\Z82UNBI2\\Hu et al. - 2024 - LR-Auth Towards Practical Implementation of Implicit User Authentication on Earbuds.pdf:application/pdf},
-}</t>
-  </si>
-  <si>
-    <t>@article{he_hcr-auth_2024,
-	title = {{HCR}-{Auth}: {Reliable} {Bone} {Conduction} {Earphone} {Authentication} with {Head} {Contact} {Response}},
-	volume = {8},
-	shorttitle = {{HCR}-{Auth}},
-	url = {https://dl.acm.org/doi/10.1145/3699780},
-	doi = {10.1145/3699780},
-	abstract = {Earables, or ear wearables, are increasingly being used for a variety of personal applications, prompting the development of authentication schemes to safeguard user privacy. Existing authentications are designed for traditional in-ear earphones, relying on a closed ear canal environment, which is not suited for bone conduction earphones that feature an open-ear design. In this paper, we propose HCR-Auth, a new authentication approach for bone conduction earphones based on head biometrics. It employs a modulated chirp signal, emitted by the earphone speaker, to actively sense the user's head structure, and captures the response through the earphone's accelerometer. It operates implicitly, eliminating additional efforts from the user to perform authentication. Through extensive experiments involving 60 subjects, we determine that HCR-Auth achieves a commendable balanced accuracy of 96.55\% using only 10 registration samples, proving its efficacy and resilience against potential threats. Our dataset and source codes are available at https://anonymous.4open.science/r/HCR-Auth-D43B/.},
-	number = {4},
-	urldate = {2025-11-27},
-	journal = {Proc. ACM Interact. Mob. Wearable Ubiquitous Technol.},
-	author = {He, Zhixiang and Chen, Jing and Wu, Cong and He, Kun and Du, Ruiying and Jia, Ju and Gu, Yangyang and Sun, Xiping},
-	year = {2024},
-	pages = {208:1--208:27},
-	file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\E28CBSNV\\He et al. - 2024 - HCR-Auth Reliable Bone Conduction Earphone Authentication with Head Contact Response.pdf:application/pdf},
-}</t>
-  </si>
-  <si>
-    <t>@article{he_headsonic_2025,
-	title = {{HeadSonic}: {Usable} {Bone} {Conduction} {Earphone} {Authentication} via {Head}-{Conducted} {Sounds}},
-	volume = {24},
-	issn = {1558-0660},
-	shorttitle = {{HeadSonic}},
-	url = {https://ieeexplore.ieee.org/document/10925832},
-	doi = {10.1109/TMC.2025.3551272},
-	abstract = {Earables (ear wearables) are rapidly emerging as a new platform encompassing a diverse of personal applications, prompting the development of authentication schemes to protect user privacy. Existing earable authentication methods are all specifically designed for air-conduction earphones, which are not suited for bone conduction earphones (BCEs) that rely on bone conduction mechanisms. In this paper, we propose HeadSonic, a usable BCE authentication system based on the unique head-conducted sounds, which can be acquired when the user wears the BCE device. Specifically, the system emits a millisecond-level sound to initiate the authentication session. The signal captured by the BCE microphone is propagated through the user's head, which is unique in density, geometry, and bone-tissue ratio. It operates implicitly, while maintaining robustness across different behaviors. Extensive experiments involving 60 subjects demonstrate that HeadSonic achieves a commendable balanced accuracy of 96.59\%, proving its efficacy and resilience against replay and synthesis attacks. Our dataset and source codes are available at https://anonymous.4open.science/r/HeadSonic-1CE4.},
-	number = {9},
-	urldate = {2025-11-28},
-	journal = {IEEE Transactions on Mobile Computing},
-	author = {He, Zhixiang and Chen, Jing and He, Kun and Gu, Yangyang and Deng, Qiyi and Zhang, Zijian and Du, Ruiying and Zhao, Qingchuan and Wu, Cong},
-	month = sep,
-	year = {2025},
-	keywords = {Ear, Authentication, biometrics, Biometrics, Sensors, Microphones, Acoustics, Mobile computing, acoustic sensing, Geometry, Noise, Reflection, Wearable authentication},
-	pages = {7914--7928},
-	file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\F9ZX3AAE\\He et al. - 2025 - HeadSonic Usable Bone Conduction Earphone Authentication via Head-Conducted Sounds.pdf:application/pdf},
-}</t>
-  </si>
-  <si>
-    <t>@article{han_exploring_2024,
-	title = {Exploring {Earable}-{Based} {Passive} {User} {Authentication} via {Interpretable} {In}-{Ear} {Breathing} {Biometrics}},
-	volume = {23},
-	issn = {1558-0660},
-	url = {https://ieeexplore.ieee.org/abstract/document/10663927},
-	doi = {10.1109/TMC.2024.3453412},
-	abstract = {As earable devices have become indispensable smart devices in people's lives, earable-based user authentication has gradually attracted widespread attention. In our work, we explore novel in-ear breathing biometrics and design an earable-based authentication approach, named BreathSign, which takes advantage of inward-facing microphones on commercial earphones to capture in-ear breathing sounds for passive authentication. To expand the differences among individuals, we model the process of breathing sound generation, transmission, and reception. Based on that, we derive hard-to-forge physical-level features from in-ear breathing sounds as biometrics. Furthermore, to eliminate the impact of breathing behavioral patterns (e.g., duration and intensity), we design a triple network model to extract breathing behavior-independent features and design an online user template update mechanism for long-term authentication. Extensive experiments with 35 healthy subjects have been conducted to evaluate the performance of BreathSign. The results show that our system achieves the average authentication accuracy of 93.15\%, 98.06\%, and 99.74\% via one, five, and nine breathing cycles, respectively. Regarding the resistance of spoofing attacks, BreathSign could achieve an average EER of approximately 3.5\%. Compared with other behavior-based authentication schemes, BreathSign does not require users to perform complex movements or postures but only effortless breathing for authentication and can be easily implemented on commercial earphones with high usability and enhanced security.},
-	number = {12},
-	urldate = {2025-11-27},
-	journal = {IEEE Transactions on Mobile Computing},
-	author = {Han, Feiyu and Yang, Panlong and Feng, Yuanhao and Du, Haohua and Li, Xiang-Yang},
-	month = dec,
-	year = {2024},
-	keywords = {Ear, Irrigation, Authentication, Feature extraction, Biometrics, Headphones, Microphones, Breathing biometrics, earable sensing, in-ear breathing sounds, passive authentication},
-	pages = {15238--15255},
-	file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\MNV4XV7B\\Han et al. - 2024 - Exploring Earable-Based Passive User Authentication via Interpretable In-Ear Breathing Biometrics.pdf:application/pdf},
-}</t>
-  </si>
-  <si>
-    <t>@article{gao_quick-pass_2025,
-	title = {Quick-pass {Continuous} {Authentication} with {Real}-time {Biometrics} {Extraction} on {COTS} {Earphones} {Using} {Out}-ear {Microphones}},
-	issn = {1558-0660},
-	url = {https://ieeexplore.ieee.org/document/11153058},
-	doi = {10.1109/TMC.2025.3606846},
-	abstract = {Continuous authentication is increasingly critical for cyber security. However, existing approaches are time-consuming due to their simplistic signal modulation and low efficiency in feature extraction. In this paper, we propose a continuous authentication technique, OnePiece. OnePiece is free from the requirement of in-ear microphones, which are necessary for existing earphone authentication systems. It exploits out-ear microphones for biometrics extraction, which are ubiquitous on off-the-shelf earphones. We analyze the acoustic response model of ears towards out-ear microphones via the air, which is different from that towards in-ear microphones. A frequency-varying ultrasonic modulation scheme is proposed to characterize in-depth ear biometrics in user-friendly, error-free, and time-efficient ways. Therefore, OnePiece enables quick-pass authentication once users wear the earphones, followed by continuous authentication covering the whole course. Moreover, we propose a wake-up mechanism to reduce the consumed power, which addresses the key power consumption issue in ultrasonic sensing techniques. Particularly, OnePiece can be smoothly deployed on off-the-shelf wired and wireless earphones. It performs good cross-device performance in which users just register only once. Extensive evaluations are conducted to validate its effectiveness under real-world scenarios.},
-	urldate = {2025-11-28},
-	journal = {IEEE Transactions on Mobile Computing},
-	author = {Gao, Ming and Chen, Jiatong and Tong, Xin and Ye, Ruitong and Chen, Yike and Xiao, Fu and Han, Jinsong},
-	year = {2025},
-	keywords = {Ear, Authentication, Biometrics, Headphones, Internet of Things, Sensors, Wireless sensor networks, Acoustic Sensing, Microphones, Acoustics, Continuous User Authentication, Earable Sensing, Ultrasonic imaging},
-	pages = {1--18},
-	file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\SRFMZJ7R\\Gao et al. - 2025 - Quick-pass Continuous Authentication with Real-time Biometrics Extraction on COTS Earphones Using Ou.pdf:application/pdf},
-}</t>
-  </si>
-  <si>
-    <t>@inproceedings{duan_f2key_2024,
-	address = {New York, NY, USA},
-	series = {{MOBISYS} '24},
-	title = {{F2Key}: {Dynamically} {Converting} {Your} {Face} into a {Private} {Key} {Based} on {COTS} {Headphones} for {Reliable} {Voice} {Interaction}},
-	isbn = {979-8-4007-0581-6},
-	shorttitle = {{F2Key}},
-	url = {https://dl.acm.org/doi/10.1145/3643832.3661860},
-	doi = {10.1145/3643832.3661860},
-	abstract = {In this paper, we proposed F2Key, the first earable physical security system based on commercial off-the-shelf headphones. F2Key enables impactful applications, such as enhancing voiceprint-based authentication systems, reliable voice assistants, audio deepfake defense, and the legal validity of artifacts. The key idea of F2Key is to establish a stable acoustic sensing field across the user's face and embed the user's facial structures and articulatory habits into a user-specific generative model that serves as a private key. The private key can decrypt the Channel Impulse Response (CIR) profiles provided by the acoustic sensing field into an inferred spectrogram that can match the real one calculated from the corresponding speech, provided that the user's CIR-spectrogram mapping relationship is consistent with the one embedded in the generative model. Extensive experiments demonstrate that F2Key resists 99.9\%, 96.4\%, and 95.3\% of speech replay attacks, mimicry attacks, and hybrid attacks, respectively. We discussed and evaluated F2Key from different perspectives, such as the health consideration and identical twins study, to show the practicality and reliability.},
-	urldate = {2025-11-26},
-	booktitle = {Proceedings of the 22nd {Annual} {International} {Conference} on {Mobile} {Systems}, {Applications} and {Services}},
-	publisher = {Association for Computing Machinery},
-	author = {Duan, Di and Sun, Zehua and Ni, Tao and Li, Shuaicheng and Jia, Xiaohua and Xu, Weitao and Li, Tianxing},
-	year = {2024},
-	pages = {127--140},
-	file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\93ZRMKYL\\Duan et al. - 2024 - F2Key Dynamically Converting Your Face into a Private Key Based on COTS Headphones for Reliable Voi.pdf:application/pdf},
-}</t>
-  </si>
-  <si>
-    <t>@inproceedings{choi_earppg_2023,
-	address = {New York, NY, USA},
-	series = {{IUI} '23},
-	title = {{EarPPG}: {Securing} {Your} {Identity} with {Your} {Ears}},
-	isbn = {979-8-4007-0106-1},
-	shorttitle = {{EarPPG}},
-	url = {https://dl.acm.org/doi/10.1145/3581641.3584070},
-	doi = {10.1145/3581641.3584070},
-	abstract = {Wearable devices have become indispensable gadgets in people’s daily lives nowadays; especially wireless earphones have experienced unprecedented growth in recent years, which lead to increasing interest and explorations of user authentication techniques. Conventional user authentication methods embedded in wireless earphones that use microphones or other modalities are vulnerable to environmental factors, such as loud noises or occlusions. To address this limitation, we introduce EarPPG, a new biometric modality that takes advantage of the unique in-ear photoplethysmography (PPG) signals, altered by a user’s unique speaking behaviors. When the user is speaking, muscle movements cause changes in the blood vessel geometry, inducing unique PPG signal variations. As speaking behaviors and PPG signals are unique, the EarPPG combines both biometric traits and presents a secure and obscure authentication solution. The system first detects and segments EarPPG signals and proceeds to extract effective features to construct a user authentication model with the 1D ReGRU network. We conducted comprehensive real-world evaluations with 25 human participants and achieved 94.84\% accuracy, 0.95 precision, recall, and f1-score, respectively. Moreover, considering the practical implications, we conducted several extensive in-the-wild experiments, including body motions, occlusions, lighting, and permanence. Overall outcomes of this study possess the potential to be embedded in future smart earable devices.},
-	urldate = {2025-11-26},
-	booktitle = {Proceedings of the 28th {International} {Conference} on {Intelligent} {User} {Interfaces}},
-	publisher = {Association for Computing Machinery},
-	author = {Choi, Seokmin and Yim, Junghwan and Jin, Yincheng and Gao, Yang and Li, Jiyang and Jin, Zhanpeng},
-	year = {2023},
-	pages = {835--849},
-	file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\A7VLR2BX\\Choi et al. - 2023 - EarPPG Securing Your Identity with Your Ears.pdf:application/pdf},
-}</t>
-  </si>
-  <si>
-    <t>@article{cao_enabling_2025,
-	title = {Enabling {Passive} {User} {Authentication} via {Heart} {Sounds} on {In}-{Ear} {Microphones}},
-	volume = {22},
-	issn = {1941-0018},
-	url = {https://ieeexplore.ieee.org/document/10604926},
-	doi = {10.1109/TDSC.2024.3429574},
-	abstract = {Biometrics has been increasingly integrated into wearables for enhanced data security in recent years. Meanwhile, wearable popularity offers a unique chance to capture novel biometrics via embedded sensors. In this article, we study new intracorporal biometrics combining the uniqueness of heart motion, bone conduction, and body asymmetry. Specifically, we introduce HeartPrint, a passive yet secure user authentication system exploiting the bone-conducted heart sounds captured by (widely available) dual in-ear microphones (IEMs). To eliminate interference, we devise a novel method combining modified non-negative matrix factorization and adaptive filtering. This extracts clean heart sounds while addressing interference of body sounds and audio produced by the earphones. We further explore the uniqueness of IEM-recorded heart sounds in three aspects to extract a novel biometric representation, based on which HeartPrint leverages a convolutional neural model equipped with a continual learning method to achieve accurate authentication under drifting body conditions. Furthermore, user-friendly registration and energy-effective authentication are facilitated by a data augmentation method using transformer-based GAN and an authentication interval control method. Extensive experiments with 45 participants confirm that HeartPrint can achieve 1.6\% FAR and 1.8\% FRR, while effectively coping with major attacks, complicated interference, and hardware diversity, while exhibiting robustness in real-world environments.},
-	number = {2},
-	urldate = {2025-11-28},
-	journal = {IEEE Transactions on Dependable and Secure Computing},
-	author = {Cao, Yetong and Cai, Chao and Li, Fan and Chen, Zhe and Luo, Jun},
-	month = mar,
-	year = {2025},
-	keywords = {Ear, Authentication, Headphones, Heart, Biometrics (access control), ANC earphones, Bones, in-ear microphones, neural network, Passive authentication, Phonocardiography},
-	pages = {1195--1209},
-	file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\G65NY2B6\\Cao et al. - 2025 - Enabling Passive User Authentication via Heart Sounds on In-Ear Microphones.pdf:application/pdf},
-}</t>
-  </si>
-  <si>
-    <t>@article{bi_smartear_2022,
-	title = {{SmartEar}: {Rhythm}-{Based} {Tap} {Authentication} {Using} {Earphone} in {Information}-{Centric} {Wireless} {Sensor} {Network}},
-	volume = {9},
-	issn = {2327-4662},
-	shorttitle = {{SmartEar}},
-	url = {https://ieeexplore.ieee.org/document/9367286},
-	doi = {10.1109/JIOT.2021.3063479},
-	abstract = {The rapid development of the information-centric wireless sensor network (ICWSN) has solved the challenges of information transmission and processing caused by the accelerated growth of wearable devices and the wide deployment of the Internet of Things (IoT) recently. The privacy security is also a growing problem. The existing works use earphones, covert, and user-friendly wearable devices, for user authentication. However, some of the earphone-based authentication solutions need to customize special earphones, which are not universal. Other solutions use microphones and speakers of earphones for authentication, which are susceptible to changes in the auricle’s internal environment, resulting in a decline in performance. To solve this problem, a new authentication solution based on the existing commercial earphones is proposed to authenticate a user by tapping on the earphone rhythmically. This rhythmic tap behavior causes a change of the signal waveform of the built-in accelerometer in the earphone. Based on this, we design a pipeline to authenticate the user’s identity. We first design an event detection algorithm to segment the tap signal accurately. Then, we use the global features calculated based on the event detection algorithm and local features extracted from the convolutional neural network (CNN) for building an authentication model using the Naive Bayes (NB) classifier. Finally, 20 users are recruited to evaluate the experiment and the recognition accuracy reaches 98\%. Moreover, we extend the experiment to prove that it has a good performance against the different attacks and is robust in different scenarios.},
-	number = {2},
-	urldate = {2025-11-27},
-	journal = {IEEE Internet of Things Journal},
-	author = {Bi, Hongliang and Sun, Yuanyuan and Liu, Jiajia and Cao, Lihao},
-	month = jan,
-	year = {2022},
-	keywords = {Authentication, Accelerometer, Accelerometers, earphone, Euclidean distance, Headphones, Internet of Things, Probability density function, Rhythm, tap gesture, user authentication},
-	pages = {885--896},
-	file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\UZ6JC5J2\\Bi et al. - 2022 - SmartEar Rhythm-Based Tap Authentication Using Earphone in Information-Centric Wireless Sensor Netw.pdf:application/pdf},
-}</t>
-  </si>
-  <si>
-    <t>@article{amesaka_earlock_2025,
-	title = {{EarLock}: {Personal} {Authentication} {System} for {Hearables} {Using} {Sound} {Leakage} {Signals}},
-	volume = {24},
-	issn = {1558-0660},
-	shorttitle = {{EarLock}},
-	url = {https://ieeexplore.ieee.org/document/10879366},
-	doi = {10.1109/TMC.2025.3540584},
-	abstract = {Earphone-type wearable devices, also known as “hearables,” will have many functions in the future. Some of those functions will require authentication of the wearer for access to the user's privacy information or settlement of payments. In this study, we propose a new personal authentication system for hearables called EarLock. EarLock authenticates the wearer by acquiring and analyzing ear canal and auricle shape information using sound leakage from the device. The system can be implemented using a speaker and external microphone that are highly compatible with hearables. We implemented three prototype devices and investigated EarLock's authentication performance under various practical scenarios, including walking conditions, noisy environments, and situations with object interference. Experimental results showed that the in-ear, open-ear, and bone-conduction devices achieved balanced accuracy (BAC) scores of 87.2–93.7\%, 83.4–94.7\%, and 85.9–90.0\%.},
-	number = {7},
-	urldate = {2025-11-28},
-	journal = {IEEE Transactions on Mobile Computing},
-	author = {Amesaka, Takashi and Watanabe, Hiroki and Sugiura, Yuta and Sugimoto, Masanori and Shizuki, Buntarou},
-	month = jul,
-	year = {2025},
-	keywords = {Ear, Irrigation, Authentication, Electroencephalography, Biometrics, Shape, Microphones, Acoustics, authentication, active acoustic sensing, ear biometrics, Hearables, Legged locomotion, Mobile computing, sound leakage},
-	pages = {6183--6196},
-	file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\6V24CG7D\\Amesaka et al. - 2025 - EarLock Personal Authentication System for Hearables Using Sound Leakage Signals.pdf:application/pdf},
-}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@article{wang_eardynamic_2021,
- title = {{EarDynamic}: {An} {Ear} {Canal} {Deformation} {Based} {Continuous} {User} {Authentication} {Using} {In}-{Ear} {Wearables}},
- volume = {5},
- shorttitle = {{EarDynamic}},
- url = {https://dl.acm.org/doi/10.1145/3448098},
- doi = {10.1145/3448098},
- abstract = {Biometric-based authentication is gaining increasing attention for wearables and mobile applications. Meanwhile, the growing adoption of sensors in wearables also provides opportunities to capture novel wearable biometrics. In this work, we propose EarDynamic, an ear canal deformation based user authentication using in-ear wearables. EarDynamic provides continuous and passive user authentication and is transparent to users. It leverages ear canal deformation that combines the unique static geometry and dynamic motions of the ear canal when the user is speaking for authentication. It utilizes an acoustic sensing approach to capture the ear canal deformation with the built-in microphone and speaker of the in-ear wearable. Specifically, it first emits well-designed inaudible beep signals and records the reflected signals from the ear canal. It then analyzes the reflected signals and extracts fine-grained acoustic features that correspond to the ear canal deformation for user authentication. Our extensive experimental evaluation shows that EarDynamic can achieve a recall of 97.38\% and an F1 score of 96.84\%. Results also show that our system works well under different noisy environments with various daily activities.},
- number = {1},
+    <t>@inproceedings{curran_one-step_2017,
+ address = {New York, NY, USA},
+ series = {{UbiComp} '17},
+ title = {One-step, three-factor authentication in a single earpiece},
+ isbn = {978-1-4503-5190-4},
+ url = {https://dl.acm.org/doi/10.1145/3123024.3123087},
+ doi = {10.1145/3123024.3123087},
+ abstract = {Multifactor authentication presents a robust security method, but typically requires multiple steps on the part of the user resulting in a high cost to usability and limiting adoption. Furthermore, a truly usable system must be unobtrusive and inconspicuous. Here, we present a system that provides all three factors of authentication (knowledge, possession, and inherence) in a single step in the form of an earpiece which implements brain-based authentication via custom-fit, in-ear electroencephalography (EEG). We demonstrate its potential by collecting EEG data using manufactured custom-fit earpieces with embedded electrodes. Across 7 participants, we are able to achieve perfect performance, mean 0\% false acceptance (FAR) and 0\% false rejection rates (FRR), using participants' best performing tasks collected in one session by one earpiece with three electrodes. Our results indicate that a single earpiece with embedded electrodes could provide a discreet, convenient, and robust method for secure one-step, three-factor authentication.},
  urldate = {2026-01-16},
- journal = {Proc. ACM Interact. Mob. Wearable Ubiquitous Technol.},
- author = {Wang, Zi and Tan, Sheng and Zhang, Linghan and Ren, Yili and Wang, Zhi and Yang, Jie},
- year = {2021},
- pages = {39:1--39:27},
- file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\H68YIYBM\\Wang et al. - 2021 - EarDynamic An Ear Canal Deformation Based Continuous User Authentication Using In-Ear Wearables.pdf:application/pdf},
-}
-</t>
+ booktitle = {Proceedings of the 2017 {ACM} {International} {Joint} {Conference} on {Pervasive} and {Ubiquitous} {Computing} and {Proceedings} of the 2017 {ACM} {International} {Symposium} on {Wearable} {Computers}},
+ publisher = {Association for Computing Machinery},
+ author = {Curran, Max T. and Merrill, Nick and Chuang, John and Gandhi, Swapan},
+ year = {2017},
+ pages = {21--24},
+ file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\7FT9XIRU\\Curran et al. - 2017 - One-step, three-factor authentication in a single earpiece.pdf:application/pdf},
+}</t>
   </si>
   <si>
     <t>@article{nakamura_-ear_2018,
@@ -673,24 +179,58 @@
 </t>
   </si>
   <si>
-    <t>@article{liu_earprint_2014,
- title = {Earprint: {Transient} {Evoked} {Otoacoustic} {Emission} for {Biometrics}},
- volume = {9},
- issn = {1556-6021},
- shorttitle = {Earprint},
- url = {https://ieeexplore.ieee.org/document/6914592},
- doi = {10.1109/TIFS.2014.2361205},
- abstract = {Biometrics is attracting increasing attention in privacy and security concerned issues, such as access control and remote financial transaction. However, advanced forgery and spoofing techniques are threatening the reliability of conventional biometric modalities. This has been motivating our investigation of a novel yet promising modality transient evoked otoacoustic emission (TEOAE), which is an acoustic response generated from cochlea after a click stimulus. Unlike conventional modalities that are easily accessible or captured, TEOAE is naturally immune to replay and falsification attacks as a physiological outcome from human auditory system. In this paper, we resort to wavelet analysis to derive the time-frequency representation of such nonstationary signal, which reveals individual uniqueness and long-term reproducibility. A machine learning technique linear discriminant analysis is subsequently utilized to reduce intrasubject variability and further capture intersubject differentiation features. Considering practical application, we also introduce a complete framework of the biometric system in both verification and identification modes. Comparative experiments on a TEOAE data set of biometric setting show the merits of the proposed method. Performance is further improved with fusion of information from both ears.},
- number = {12},
+    <t xml:space="preserve">@article{gao_earecho_2019,
+ title = {{EarEcho}: {Using} {Ear} {Canal} {Echo} for {Wearable} {Authentication}},
+ volume = {3},
+ shorttitle = {{EarEcho}},
+ url = {https://dl.acm.org/doi/10.1145/3351239},
+ doi = {10.1145/3351239},
+ abstract = {Smart wearable devices have recently become one of the major technological trends and been widely adopted by the general public. Wireless earphones, in particular, have seen a skyrocketing growth due to its great usability and convenience. With the goal of seeking a more unobtrusive wearable authentication method that the users can easily use and conveniently access, in this study we present EarEcho as a novel, affordable, user-friendly biometric authentication solution. EarEcho takes advantages of the unique physical and geometrical characteristics of human ear canal and assesses the content-free acoustic features of in-ear sound waves for user authentication in a wearable and mobile manner. We implemented the proposed EarEcho on a proof-of-concept prototype and tested it among 20 subjects under diverse application scenarios. We can achieve a recall of 94.19\% and precision of 95.16\% for one-time authentication, while a recall of 97.55\% and precision of 97.57\% for continuous authentication. EarEcho has demonstrated its stability over time and robustness to cope with the uncertainties on the varying background noises, body motions, and sound pressure levels.},
+ number = {3},
  urldate = {2026-01-16},
- journal = {IEEE Transactions on Information Forensics and Security},
- author = {Liu, Yuxi and Hatzinakos, Dimitrios},
- month = dec,
- year = {2014},
- keywords = {Feature extraction, Biometrics (access control), Auditory system, biometric fusion, linear discriminant analysis, Linear discriminant analysis, Robust biometric modality, Robust Biometric Modality, time-frequency analysis, Time-frequency analysis, Time-frequency Analysis, transient evoked otoacoustic emission, Transient Evoked Otoacoustic Emission},
- pages = {2291--2301},
- file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\ST468TL4\\Liu and Hatzinakos - 2014 - Earprint Transient Evoked Otoacoustic Emission for Biometrics.pdf:application/pdf},
-}</t>
+ journal = {Proc. ACM Interact. Mob. Wearable Ubiquitous Technol.},
+ author = {Gao, Yang and Wang, Wei and Phoha, Vir V. and Sun, Wei and Jin, Zhanpeng},
+ year = {2019},
+ pages = {81:1--81:24},
+ file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\FHMS8BMN\\Gao et al. - 2019 - EarEcho Using Ear Canal Echo for Wearable Authentication.pdf:application/pdf},
+}
+</t>
+  </si>
+  <si>
+    <t>@inproceedings{clarke_motion_2020,
+ address = {New York, NY, USA},
+ series = {{MUM} '20},
+ title = {Motion {Coupling} of {Earable} {Devices} in {Camera} {View}},
+ isbn = {978-1-4503-8870-2},
+ url = {https://dl.acm.org/doi/10.1145/3428361.3428470},
+ doi = {10.1145/3428361.3428470},
+ abstract = {Earables, earphones augmented with inertial sensors and real-time data accessibility, provide the opportunity for private audio channels in public settings. One of the main challenges of achieving this goal is to correctly associate which device belongs to which user without prior information. In this paper, we explore how motion of an earable, as measured by the on-board accelerometer, can be correlated against detected faces from a webcam to accurately match which user is wearing the device. We conduct a data collection and explore which type of user movement can be accurately detected using this approach, and investigate how varying the speed of the movement affects detection rates. Our results show that the approach achieves greater detection results for faster movements, and that it can differentiate the same movement across different participants with a detection rate of 86\%, increasing to 92\% when differentiating a movement against others.},
+ urldate = {2026-01-17},
+ booktitle = {Proceedings of the 19th {International} {Conference} on {Mobile} and {Ubiquitous} {Multimedia}},
+ publisher = {Association for Computing Machinery},
+ author = {Clarke, Christopher and Ehrich, Peter and Gellersen, Hans},
+ year = {2020},
+ pages = {13--17},
+ file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\LKE6Y3Y4\\Clarke et al. - 2020 - Motion Coupling of Earable Devices in Camera View.pdf:application/pdf},
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@article{wang_eardynamic_2021,
+ title = {{EarDynamic}: {An} {Ear} {Canal} {Deformation} {Based} {Continuous} {User} {Authentication} {Using} {In}-{Ear} {Wearables}},
+ volume = {5},
+ shorttitle = {{EarDynamic}},
+ url = {https://dl.acm.org/doi/10.1145/3448098},
+ doi = {10.1145/3448098},
+ abstract = {Biometric-based authentication is gaining increasing attention for wearables and mobile applications. Meanwhile, the growing adoption of sensors in wearables also provides opportunities to capture novel wearable biometrics. In this work, we propose EarDynamic, an ear canal deformation based user authentication using in-ear wearables. EarDynamic provides continuous and passive user authentication and is transparent to users. It leverages ear canal deformation that combines the unique static geometry and dynamic motions of the ear canal when the user is speaking for authentication. It utilizes an acoustic sensing approach to capture the ear canal deformation with the built-in microphone and speaker of the in-ear wearable. Specifically, it first emits well-designed inaudible beep signals and records the reflected signals from the ear canal. It then analyzes the reflected signals and extracts fine-grained acoustic features that correspond to the ear canal deformation for user authentication. Our extensive experimental evaluation shows that EarDynamic can achieve a recall of 97.38\% and an F1 score of 96.84\%. Results also show that our system works well under different noisy environments with various daily activities.},
+ number = {1},
+ urldate = {2026-01-16},
+ journal = {Proc. ACM Interact. Mob. Wearable Ubiquitous Technol.},
+ author = {Wang, Zi and Tan, Sheng and Zhang, Linghan and Ren, Yili and Wang, Zhi and Yang, Jie},
+ year = {2021},
+ pages = {39:1--39:27},
+ file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\H68YIYBM\\Wang et al. - 2021 - EarDynamic An Ear Canal Deformation Based Continuous User Authentication Using In-Ear Wearables.pdf:application/pdf},
+}
+</t>
   </si>
   <si>
     <t>@inproceedings{liu_mandipass_2021,
@@ -710,24 +250,6 @@
  pages = {674--684},
  file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\WAFDGKMI\\Liu et al. - 2021 - MandiPass Secure and Usable User Authentication via Earphone IMU.pdf:application/pdf},
 }</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@article{gao_earecho_2019,
- title = {{EarEcho}: {Using} {Ear} {Canal} {Echo} for {Wearable} {Authentication}},
- volume = {3},
- shorttitle = {{EarEcho}},
- url = {https://dl.acm.org/doi/10.1145/3351239},
- doi = {10.1145/3351239},
- abstract = {Smart wearable devices have recently become one of the major technological trends and been widely adopted by the general public. Wireless earphones, in particular, have seen a skyrocketing growth due to its great usability and convenience. With the goal of seeking a more unobtrusive wearable authentication method that the users can easily use and conveniently access, in this study we present EarEcho as a novel, affordable, user-friendly biometric authentication solution. EarEcho takes advantages of the unique physical and geometrical characteristics of human ear canal and assesses the content-free acoustic features of in-ear sound waves for user authentication in a wearable and mobile manner. We implemented the proposed EarEcho on a proof-of-concept prototype and tested it among 20 subjects under diverse application scenarios. We can achieve a recall of 94.19\% and precision of 95.16\% for one-time authentication, while a recall of 97.55\% and precision of 97.57\% for continuous authentication. EarEcho has demonstrated its stability over time and robustness to cope with the uncertainties on the varying background noises, body motions, and sound pressure levels.},
- number = {3},
- urldate = {2026-01-16},
- journal = {Proc. ACM Interact. Mob. Wearable Ubiquitous Technol.},
- author = {Gao, Yang and Wang, Wei and Phoha, Vir V. and Sun, Wei and Jin, Zhanpeng},
- year = {2019},
- pages = {81:1--81:24},
- file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\FHMS8BMN\\Gao et al. - 2019 - EarEcho Using Ear Canal Echo for Wearable Authentication.pdf:application/pdf},
-}
-</t>
   </si>
   <si>
     <t>@article{gao_voice_2021,
@@ -786,6 +308,45 @@
 </t>
   </si>
   <si>
+    <t>@article{wang_toothsonic_2022,
+ title = {{ToothSonic}: {Earable} {Authentication} via {Acoustic} {Toothprint}},
+ volume = {6},
+ shorttitle = {{ToothSonic}},
+ url = {https://dl.acm.org/doi/10.1145/3534606},
+ doi = {10.1145/3534606},
+ abstract = {Earables (ear wearables) are rapidly emerging as a new platform encompassing a diverse range of personal applications. The traditional authentication methods hence become less applicable and inconvenient for earables due to their limited input interface. Nevertheless, earables often feature rich around-the-head sensing capability that can be leveraged to capture new types of biometrics. In this work, we propose ToothSonic that leverages the toothprint-induced sonic effect produced by a user performing teeth gestures for earable authentication. In particular, we design representative teeth gestures that can produce effective sonic waves carrying the information of the toothprint. To reliably capture the acoustic toothprint, it leverages the occlusion effect of the ear canal and the inward-facing microphone of the earables. It then extracts multi-level acoustic features to reflect the intrinsic toothprint information for authentication. The key advantages of ToothSonic are that it is suitable for earables and is resistant to various spoofing attacks as the acoustic toothprint is captured via the user's private teeth-ear channel that modulates and encrypts the sonic waves. Our experiment studies with 25 participants show that ToothSonic achieves up to 95\% accuracy with only one of the users' tooth gestures.},
+ number = {2},
+ urldate = {2025-11-26},
+ journal = {Proc. ACM Interact. Mob. Wearable Ubiquitous Technol.},
+ author = {Wang, Zi and Ren, Yili and Chen, Yingying and Yang, Jie},
+ year = {2022},
+ pages = {78:1--78:24},
+ annote = {“a secure earable authentication system that leverages the toothprint-induced sonic waves for user authentication” (Wang et al., 2022, p. 20)
+},
+ file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\H7ZTB3YV\\Wang et al. - 2022 - ToothSonic Earable Authentication via Acoustic Toothprint.pdf:application/pdf},
+}</t>
+  </si>
+  <si>
+    <t>@article{bi_smartear_2022,
+ title = {{SmartEar}: {Rhythm}-{Based} {Tap} {Authentication} {Using} {Earphone} in {Information}-{Centric} {Wireless} {Sensor} {Network}},
+ volume = {9},
+ issn = {2327-4662},
+ shorttitle = {{SmartEar}},
+ url = {https://ieeexplore.ieee.org/document/9367286},
+ doi = {10.1109/JIOT.2021.3063479},
+ abstract = {The rapid development of the information-centric wireless sensor network (ICWSN) has solved the challenges of information transmission and processing caused by the accelerated growth of wearable devices and the wide deployment of the Internet of Things (IoT) recently. The privacy security is also a growing problem. The existing works use earphones, covert, and user-friendly wearable devices, for user authentication. However, some of the earphone-based authentication solutions need to customize special earphones, which are not universal. Other solutions use microphones and speakers of earphones for authentication, which are susceptible to changes in the auricle’s internal environment, resulting in a decline in performance. To solve this problem, a new authentication solution based on the existing commercial earphones is proposed to authenticate a user by tapping on the earphone rhythmically. This rhythmic tap behavior causes a change of the signal waveform of the built-in accelerometer in the earphone. Based on this, we design a pipeline to authenticate the user’s identity. We first design an event detection algorithm to segment the tap signal accurately. Then, we use the global features calculated based on the event detection algorithm and local features extracted from the convolutional neural network (CNN) for building an authentication model using the Naive Bayes (NB) classifier. Finally, 20 users are recruited to evaluate the experiment and the recognition accuracy reaches 98\%. Moreover, we extend the experiment to prove that it has a good performance against the different attacks and is robust in different scenarios.},
+ number = {2},
+ urldate = {2025-11-27},
+ journal = {IEEE Internet of Things Journal},
+ author = {Bi, Hongliang and Sun, Yuanyuan and Liu, Jiajia and Cao, Lihao},
+ month = jan,
+ year = {2022},
+ keywords = {Authentication, Accelerometer, Accelerometers, earphone, Euclidean distance, Headphones, Internet of Things, Probability density function, Rhythm, tap gesture, user authentication},
+ pages = {885--896},
+ file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\UZ6JC5J2\\Bi et al. - 2022 - SmartEar Rhythm-Based Tap Authentication Using Earphone in Information-Centric Wireless Sensor Netw.pdf:application/pdf},
+}</t>
+  </si>
+  <si>
     <t>@article{ding_leakage_2022,
  title = {Leakage or {Identification}: {Behavior}-irrelevant {User} {Identification} {Leveraging} {Leakage} {Current} on {Laptops}},
  volume = {5},
@@ -803,106 +364,544 @@
 }</t>
   </si>
   <si>
-    <t>@inproceedings{derawi_biometric_2016,
- title = {Biometric acoustic ear recognition},
- url = {https://ieeexplore.ieee.org/document/7835597},
- doi = {10.1109/BIOSMART.2016.7835597},
- abstract = {This paper deals with the holistic development of a biometric system based on acoustic ear recognition. Its main purpose is to map one aspects within acoustic ear recognition, namely the performance of the ear characteristics bands and peaks. 50 subjects have participated in experiments collecting biometric samples. The measuring device composed of a pair of headphones with an integrated microphone as sensor. Several methods have been utilized for feature extraction, and various types of distance metrics and classifiers have been employed.},
- urldate = {2026-01-16},
- booktitle = {2016 {International} {Conference} on {Bio}-engineering for {Smart} {Technologies} ({BioSMART})},
- author = {Derawi, Mohammad},
+    <t>@article{zou_beyond_2023,
+ title = {Beyond {Legitimacy}, {Also} {With} {Identity}: {Your} {Smart} {Earphones} {Know} {Who} {You} {Are} {Quietly}},
+ volume = {22},
+ issn = {1558-0660},
+ shorttitle = {Beyond {Legitimacy}, {Also} {With} {Identity}},
+ url = {https://ieeexplore.ieee.org/document/9647983},
+ doi = {10.1109/TMC.2021.3134654},
+ abstract = {User authentication and identification on smart devices has great significance in keeping data privacy and recommending personalized services. With the rising popularity of smart earphones recently, they open up a new world for users to enjoy music individually, but also bring about privacy concerns at the same time. Existing few research works propose positive sensing systems that emit and receive inaudible acoustic signals to authenticate users. However, they share shortcomings of intrusiveness to users, high power consumption, and purely focusing on authentication. Instead, in this paper, we propose a passive sensing system called {\textbackslash}sf EarIDEarID with low-cost customized earphones which attains user authentication and identification at once. It makes use of a embedded microphone to sense body sounds spread out through ear canals and extract ‘fingerprints’ as a novel biometric feature. With self-designed earphones, we design a deep learning-based real-time data processing pipeline and cope with external interference. Extensive experiments under different real-world settings show that {\textbackslash}sf EarIDEarID can achieve a rather low false acceptance rate of 3.4\%3.4\% for user authentication and a high F1F1 score of 95.5\%95.5\% for legitimate user identification.},
+ number = {6},
+ urldate = {2025-11-27},
+ journal = {IEEE Transactions on Mobile Computing},
+ author = {Zou, Yongpan and Lei, Haibo and Wu, Kaishun},
+ month = jun,
+ year = {2023},
+ keywords = {Ear, Irrigation, Authentication, Headphones, Sensors, deep learning, earable device, Hardware, Microphones, User authentication},
+ pages = {3179--3192},
+ file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\XAM6SIXR\\Zou et al. - 2023 - Beyond Legitimacy, Also With Identity Your Smart Earphones Know Who You Are Quietly.pdf:application/pdf},
+}</t>
+  </si>
+  <si>
+    <t>@inproceedings{wu_earae_2023,
+ title = {{EarAE}: {An} {Autoencoder} based {User} {Authentication} using {Earphones}},
+ shorttitle = {{EarAE}},
+ url = {https://ieeexplore.ieee.org/document/10233591},
+ doi = {10.1109/ICCC57788.2023.10233591},
+ abstract = {Nowadays, earphone acts an increasingly vital role in human computer interaction. Throughout this trend, earphone-based user authentication, a new modality of biometric authentication, is winning more attention. Previous research leverage ear canal related features to authenticate users. These methods establish a binary classification model, based on the assumption that the identity information of all invalid users is given. However, they may not be effective when confronting new attackers.In this paper, we propose EarAE, a lightweight auto-encoder to address this problem. The basic idea is to model the authentication as a one-class classification problem, with features of the valid user as the single training class. Specifically, during training, the ear canal features of the valid user are fed into an autoencoder and reconstructed. EarAE learns to minimize the loss function between the input and the reconstructed counterparts. In this way, valid users will have a much lower loss function score than invalid users. Finally, a threshold is set to distinguish between valid/invalid users. Experimental results show that EarAE can achieve an averaged balanced accuracy of over 96\% across 30 subjects. This demonstrates a promising prospect of EarAE to serve as a reliable means of user authentication.},
+ urldate = {2025-11-27},
+ booktitle = {2023 {IEEE}/{CIC} {International} {Conference} on {Communications} in {China} ({ICCC})},
+ author = {Wu, Yuli and He, Jing},
+ month = aug,
+ year = {2023},
+ note = {ISSN: 2377-8644},
+ keywords = {Ear, Irrigation, Authentication, Training, Headphones, Computational modeling, Acoustic Sensing, Autoencoder, Ear Canal, Human computer interaction, User Authentication},
+ pages = {1--6},
+ annote = {“the sensing process lasts one second. The probe signal is designed as a 1kHz-21kHz chirp of 50 ms length that is emitted 5 times intermittently. Meanwhile, the inear microphone captures the reflected signals from ear canal” (Wu and He, 2023, p. 2)
+},
+ file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\U9GR8ZQU\\Wu and He - 2023 - EarAE An Autoencoder based User Authentication using Earphones.pdf:application/pdf},
+}</t>
+  </si>
+  <si>
+    <t>@article{sun_earmonitor_2023,
+ title = {Earmonitor: {In}-ear {Motion}-resilient {Acoustic} {Sensing} {Using} {Commodity} {Earphones}},
+ volume = {6},
+ shorttitle = {Earmonitor},
+ url = {https://dl.acm.org/doi/10.1145/3569472},
+ doi = {10.1145/3569472},
+ abstract = {Earphones are emerging as the most popular wearable devices and there has been a growing trend in bringing intelligence to earphones. Previous efforts include adding extra sensors (e.g., accelerometer and gyroscope) or peripheral hardware to make earphones smart. These methods are usually complex in design and also incur additional cost. In this paper, we present Earmonitor, a low-cost system that uses the in-ear earphones to achieve sensing purposes. The basic idea behind Earmonitor is that each person's ear canal varies in size and shape. We therefore can extract the unique features from the ear canal-reflected signals to depict the personalized differences in ear canal geometry. Furthermore, we discover that the signal variations are also affected by the fine-grained physiological activities. We can therefore further detect the subtle heartbeat from the ear canal reflections. Experiments show that Earmonitor can achieve up to 96.4\% Balanced Accuracy (BAC) and low False Acceptance Rate (FAR) for user identification on a large-scale data of 120 subjects. For heartbeat monitoring, without any training, we propose signal processing schemes to achieve high sensing accuracy even in the most challenging scenarios when the target is walking or running.},
+ number = {4},
+ urldate = {2025-11-26},
+ journal = {Proc. ACM Interact. Mob. Wearable Ubiquitous Technol.},
+ author = {Sun, Xue and Xiong, Jie and Feng, Chao and Deng, Wenwen and Wei, Xudong and Fang, Dingyi and Chen, Xiaojiang},
+ year = {2023},
+ pages = {182:1--182:22},
+ annote = {“we propose Earmonitor hosted on low-cost earphones by simply adding a cheap in-ear microphone to achieve fine-grained sensing including user identification and heartbeat monitoring” (Sun et al., 2023, p. 20)
+},
+ file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\DQD5ICIK\\Sun et al. - 2023 - Earmonitor In-ear Motion-resilient Acoustic Sensing Using Commodity Earphones.pdf:application/pdf},
+}</t>
+  </si>
+  <si>
+    <t>@article{liu_secure_2023,
+ title = {Secure {User} {Verification} and {Continuous} {Authentication} via {Earphone} {IMU}},
+ volume = {22},
+ issn = {1558-0660},
+ url = {https://ieeexplore.ieee.org/abstract/document/9841001},
+ doi = {10.1109/TMC.2022.3193847},
+ abstract = {Biometric plays an important role in user authentication. However, the most widely used biometrics, such as facial feature and fingerprint, are easy to capture or record, and thus vulnerable to spoofing attacks. On the contrary, intracorporal biometrics, such as electrocardiography and electroencephalography, are hard to collect, and hence more secure for authentication. Unfortunately, adopting them is not user-friendly due to their complicated collection methods or inconvenient constraints on users. In this paper, we propose a novel biometric-based authentication system, namely MandiPass. MandiPass leverages inertial measurement units, which have been widely deployed in portable devices, to collect intracorporal biometric from the vibration of user's mandible. It provides not only one-time verification function but also continuous authentication function. Both the two functions are secure and user-friendly. We theoretically validate the feasibility of MandiPass and develop a series of deep learning techniques for effective biometric extraction. We also utilize a Gaussian matrix to defend against replay attacks. Extensive experiment results with 34 volunteers show that MandiPass can achieve low equal error rate, even under various harsh environments.},
+ number = {11},
+ urldate = {2025-11-27},
+ journal = {IEEE Transactions on Mobile Computing},
+ author = {Liu, Jianwei and Song, Wenfan and Shen, Leming and Han, Jinsong and Ren, Kui},
+ month = nov,
+ year = {2023},
+ keywords = {Ear, Authentication, biometrics, Headphones, Biological system modeling, Biometrics (access control), continuous authentication, inertial measurement units, Standards, User verification, Vibrations},
+ pages = {6755--6769},
+ file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\LPJJYPJA\\Liu et al. - 2023 - Secure User Verification and Continuous Authentication via Earphone IMU.pdf:application/pdf},
+}</t>
+  </si>
+  <si>
+    <t>@inproceedings{li_earpass_2023,
+ address = {New York, NY, USA},
+ series = {{UbiComp}/{ISWC} '23 {Adjunct}},
+ title = {{EarPass}: {Continuous} {User} {Authentication} with {In}-ear {PPG}},
+ isbn = {979-8-4007-0200-6},
+ shorttitle = {{EarPass}},
+ url = {https://dl.acm.org/doi/10.1145/3594739.3610670},
+ doi = {10.1145/3594739.3610670},
+ abstract = {In the rapidly expanding universe of smart IoT, earable devices, such as smart headphones and hearing aids, are gaining remarkable popularity. As we anticipate a future where a myriad of sophisticated applications—interaction, communication, health monitoring, and fitness guidance—migrate to earable devices handling sensitive and private information, the need for a robust, continuous authentication system for these devices becomes more critical than ever. Yet, current earable-based solutions, which rely predominantly on audio signals, are marred by inherent drawbacks such as privacy concerns, high costs, and noise interference. In light of these challenges, we investigate the potential of leveraging photoplethysmogram (PPG) sensors, which monitor key cardiac activities and reflect the uniqueness of an individual’s cardiac system, for earable authentication. Our study presents EarPass, an innovative ear-worn system that introduces a novel pipeline for the extraction and classification of in-ear PPG features to enable continuous user authentication. Initially, we preprocess the input in-ear PPG signals to facilitate this feature extraction and classification. Additionally, we present a method for detecting and eliminating motion artifacts (MAs) caused by head motions. Through extensive experiments, we not only demonstrate the effectiveness of our proposed design, but also establish the feasibility of using in-ear PPG for continuous user authentication—a significant stride towards more secure and efficient earable technologies.},
+ urldate = {2025-11-26},
+ booktitle = {Adjunct {Proceedings} of the 2023 {ACM} {International} {Joint} {Conference} on {Pervasive} and {Ubiquitous} {Computing} \&amp; the 2023 {ACM} {International} {Symposium} on {Wearable} {Computing}},
+ publisher = {Association for Computing Machinery},
+ author = {Li, Jiao and Liu, Yang and Li, Zhenjiang and Zhang, Jin},
+ year = {2023},
+ pages = {327--332},
+ file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\IT5YXTLN\\Li et al. - 2023 - EarPass Continuous User Authentication with In-ear PPG.pdf:application/pdf},
+}</t>
+  </si>
+  <si>
+    <t>@inproceedings{li_piezobud_2024,
+ address = {New York, NY, USA},
+ series = {{SenSys} '24},
+ title = {{PiezoBud}: {A} {Piezo}-{Aided} {Secure} {Earbud} with {Practical} {Speaker} {Authentication}},
+ isbn = {979-8-4007-0697-4},
+ shorttitle = {{PiezoBud}},
+ url = {https://dl.acm.org/doi/10.1145/3666025.3699358},
+ doi = {10.1145/3666025.3699358},
+ abstract = {With the advancement of AI-powered personal voice assistants, speaker authentication via earbuds has become increasingly vital, serving as a critical interface between users and mobile devices. However, existing audio-based speaker authentication methods fail to defend against voice spoofing threats such as replay and deep-fake attacks. To counteract these risks, we introduce PiezoBud, a pioneering multi-modal user authentication system that is truly practical and lightweight for earbuds. PiezoBud uses miniature piezoelectric sensors to detect micro-vibrations on the skin, extracting user-specific biometric data to authenticate legitimate access on the local smartphone and protect against malicious attacks. Our exploratory study, involving 85 participants, demonstrates the effectiveness of PiezoBud in various everyday scenarios, including ambient noise, body movement, and in-ear media playing. Using only 15 seconds of enrollment data, PiezoBud achieves an Equal Error Rate (EER) of 1.05\% and attain a mean authentication latency of 0.06 seconds on mobile devices. We also evaluate PiezoBud's effectiveness in countering challenging adaptive attack scenarios and its overall performance in various real-world situations. Our evaluation highlights that PiezoBud stands out as a practical, resilient, responsive, and secure option for earbuds users.},
+ urldate = {2025-11-27},
+ booktitle = {Proceedings of the 22nd {ACM} {Conference} on {Embedded} {Networked} {Sensor} {Systems}},
+ publisher = {Association for Computing Machinery},
+ author = {Li, Gen and Zeng, Huaili and Guo, Hanqing and Ren, Yidong and Dixon, Aiden and Cao, Zhichao and Li, Tianxing},
+ year = {2024},
+ pages = {564--577},
+ file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\VLIS498C\\Li et al. - 2024 - PiezoBud A Piezo-Aided Secure Earbud with Practical Speaker Authentication.pdf:application/pdf},
+}</t>
+  </si>
+  <si>
+    <t>@inproceedings{kawasaki_identification_2023,
+ title = {Identification and {Authentication} using {Clavicles}},
+ url = {https://ieeexplore.ieee.org/document/10354211/similar},
+ doi = {10.23919/SICE59929.2023.10354211},
+ abstract = {In recent years, wireless devices have become smaller and more portable. In addition, it is thought that personal identification and authentication will be necessary when they are used as independent terminals similar to smartphones. In this study, we focus on a neck-mounted earphone and propose personal identification and authentication using the acoustic characteristics of the clavicle, taking advantage of the fact that the clavicle touches the device when it is worn. Active acoustic sensing was used to measure the acoustic characteristics of the clavicle and extract its acoustic features. The accuracy was 98.8\%, and the EER was 4.0\% in five persons.},
+ urldate = {2025-11-27},
+ booktitle = {2023 62nd {Annual} {Conference} of the {Society} of {Instrument} and {Control} {Engineers} ({SICE})},
+ author = {Kawasaki, Yohei and Sugiura, Yuta},
+ month = sep,
+ year = {2023},
+ keywords = {Authentication, Feature extraction, Acoustic measurements, Wireless communication, Wireless sensor networks, Acoustics, Active acoustic sensing, authentication, identification, White noise},
+ pages = {1141--1145},
+ file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\89ILX8G8\\Kawasaki and Sugiura - 2023 - Identification and Authentication using Clavicles.pdf:application/pdf},
+}</t>
+  </si>
+  <si>
+    <t>@inproceedings{hu_lightweight_2023,
+ address = {New York, NY, USA},
+ series = {{HotMobile} '23},
+ title = {Lightweight and {Non}-{Invasive} {User} {Authentication} on {Earables}},
+ isbn = {979-8-4007-0017-0},
+ url = {https://dl.acm.org/doi/10.1145/3572864.3580332},
+ doi = {10.1145/3572864.3580332},
+ abstract = {The widespread adoption of wireless earbuds has advanced the developments in earable-based sensing in various domains like entertainment, human-computer interaction, and health monitoring. Recently, researchers have shown an increased interest in user authentication using earables. Despite the successes witnessed in acoustic probing and speech based authentication systems, this paper proposed a lightweight and non-invasive ambient sound based user authentication scheme. It employs the difference between the in-ear and out-ear sounds to estimate the individual-specific occluded ear canal transfer function (OECTF). Specifically, the \{out-ear, in-ear\} scaling factors at different frequency bands are captured via linear regression and treated as the OECTF for user authentication. The proposed system is validated using 12 subjects under six different noisy environments and achieves a Balanced Error Rate (BER) of 4.84\%. The particularly lightweight system can be easily deployed in earbuds and paves the pathway for more personalized services.},
+ urldate = {2025-11-26},
+ booktitle = {Proceedings of the 24th {International} {Workshop} on {Mobile} {Computing} {Systems} and {Applications}},
+ publisher = {Association for Computing Machinery},
+ author = {Hu, Changshuo and Ma, Xiao and Ma, Dong and Dang, Ting},
+ year = {2023},
+ pages = {36--41},
+ file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\IIFYH39D\\Hu et al. - 2023 - Lightweight and Non-Invasive User Authentication on Earables.pdf:application/pdf},
+}</t>
+  </si>
+  <si>
+    <t>@inproceedings{choi_earppg_2023,
+ address = {New York, NY, USA},
+ series = {{IUI} '23},
+ title = {{EarPPG}: {Securing} {Your} {Identity} with {Your} {Ears}},
+ isbn = {979-8-4007-0106-1},
+ shorttitle = {{EarPPG}},
+ url = {https://dl.acm.org/doi/10.1145/3581641.3584070},
+ doi = {10.1145/3581641.3584070},
+ abstract = {Wearable devices have become indispensable gadgets in people’s daily lives nowadays; especially wireless earphones have experienced unprecedented growth in recent years, which lead to increasing interest and explorations of user authentication techniques. Conventional user authentication methods embedded in wireless earphones that use microphones or other modalities are vulnerable to environmental factors, such as loud noises or occlusions. To address this limitation, we introduce EarPPG, a new biometric modality that takes advantage of the unique in-ear photoplethysmography (PPG) signals, altered by a user’s unique speaking behaviors. When the user is speaking, muscle movements cause changes in the blood vessel geometry, inducing unique PPG signal variations. As speaking behaviors and PPG signals are unique, the EarPPG combines both biometric traits and presents a secure and obscure authentication solution. The system first detects and segments EarPPG signals and proceeds to extract effective features to construct a user authentication model with the 1D ReGRU network. We conducted comprehensive real-world evaluations with 25 human participants and achieved 94.84\% accuracy, 0.95 precision, recall, and f1-score, respectively. Moreover, considering the practical implications, we conducted several extensive in-the-wild experiments, including body motions, occlusions, lighting, and permanence. Overall outcomes of this study possess the potential to be embedded in future smart earable devices.},
+ urldate = {2025-11-26},
+ booktitle = {Proceedings of the 28th {International} {Conference} on {Intelligent} {User} {Interfaces}},
+ publisher = {Association for Computing Machinery},
+ author = {Choi, Seokmin and Yim, Junghwan and Jin, Yincheng and Gao, Yang and Li, Jiyang and Jin, Zhanpeng},
+ year = {2023},
+ pages = {835--849},
+ file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\A7VLR2BX\\Choi et al. - 2023 - EarPPG Securing Your Identity with Your Ears.pdf:application/pdf},
+}</t>
+  </si>
+  <si>
+    <t>@article{zou_earprint_2024,
+ title = {{EarPrint}: {Earphone}-{Based} {Implicit} {User} {Authentication} {With} {Behavioral} and {Physiological} {Acoustics}},
+ volume = {11},
+ issn = {2327-4662},
+ shorttitle = {{EarPrint}},
+ url = {https://ieeexplore.ieee.org/document/10566858},
+ doi = {10.1109/JIOT.2024.3417622},
+ abstract = {With the increasing pervasiveness of smart earphones, it is appealing to propose more unobtrusive and convenient wearable authentication methods. Researchers have designed earphone-based authentication systems which utilize high-frequency audio signals to scan ear canal structure. Nevertheless, they possess shortcomings of low unobtrusiveness and robustness. In this article, we put forward an earphone-based passive authentication system which makes use of physiological and behavioral acoustic signals caused by a user’s natural actions, including putting on earphones and inner organs’ activities, respectively. By introducing attention mechanism into the network design, our method adaptively weighs two channel signals, and extracts stable fingerprints for different people, which relieves model retraining for unseen users and improves its scalability. We have built a real-time prototype called EarPrint by designing the earphones and a mobile application, and conducted comprehensive experiments under diverse settings. Experimental results demonstrate that EarPrint has low false acceptance rate (FAR) and equal error rate (EER) less than 1\% and 5\% in most cases, respectively.},
+ number = {19},
+ urldate = {2025-11-27},
+ journal = {IEEE Internet of Things Journal},
+ author = {Zou, Yongpan and Weng, Jianhao and Lei, Haibo and Wang, Danyang and Leung, Victor C. M. and Wu, Kaishun},
+ month = oct,
+ year = {2024},
+ keywords = {Irrigation, Authentication, Headphones, user authentication, Deep learning, Sensors, Acoustics, Smart phones, Deep metric learning (DML), Identification of persons, Physiology, smart earphones},
+ pages = {31128--31143},
+ annote = {“earphone hardware and a self-developed mobile application” (Zou et al., 2024, p. 31131)
+“two stages of which one is during putting on earphones, and the other is when earphones are worn in ears” (Zou et al., 2024, p. 31132)
+“acoustic signals are mainly caused by the rubbing between an earpiece and the ear canal during putting-on activities” (Zou et al., 2024, p. 31132)
+“activities of viscera” (Zou et al., 2024, p. 31132)
+an attention mechanism-based learning network that extracts feature representations with assigning weights automatically” (Zou et al., 2024, p. 31132)
+“to authenticate the current user, we need to calculate the similarity between his/her feature vector and the stored feature vectors of legitimate users” (Zou et al., 2024, p. 31133)
+},
+ file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\6C6CP99J\\Zou et al. - 2024 - EarPrint Earphone-Based Implicit User Authentication With Behavioral and Physiological Acoustics.pdf:application/pdf},
+}</t>
+  </si>
+  <si>
+    <t>@inproceedings{xie_earpass_2024,
+ title = {{EarPass}: {Unlock} {When} {Wearing} {Your} {Earphones}},
+ shorttitle = {{EarPass}},
+ url = {https://ieeexplore.ieee.org/document/10631065},
+ doi = {10.1109/ICDCS60910.2024.00121},
+ abstract = {With the growing reliance on digital systems in today's mobile Internet era, robust authentication methods are crucial for safeguarding personal data and controlling access to resources. Conventional methods, such as knowledge-based and biometric-based authentication, are widely used but still have some usage limitations and potential security concerns, like wearing protective suits/masks or being imitated by attackers with ulterior motives. In this paper, we propose another earphone-based authentication system, namely EarPass, that leverages users' unique head motion patterns in response to a very short period of music segment. Here, we employ a Convolutional Neural Network (CNN)-based feature extractor to capture and map distinct head motions into a well-separated latent space, achieving high-dimensional data extraction. We demonstrate the consistency, uniqueness, and robustness of head motion patterns through extensive experiments and reach a 98.2\% F1-score, indicating superior performance compared to conventional authentication methods. Additionally, EarPass is user-friendly, secure, and adaptable to various environments, including noisy and movement-oriented scenarios. By integrating the authentication system into Android devices, we showcase its real-world applicability and low energy consumption with minimal latency. The source code of EarPass will be open-source to further research and collaboration within the community.},
+ urldate = {2025-11-27},
+ booktitle = {2024 {IEEE} 44th {International} {Conference} on {Distributed} {Computing} {Systems} ({ICDCS})},
+ author = {Xie, Yanze and Gao, Mengzhen and Liu, Xiaoning and Huana, Shuo and Cui, Helei and Yu, Zhiwen and Guo, Bin},
+ month = jul,
+ year = {2024},
+ note = {ISSN: 2575-8411},
+ keywords = {Authentication, Feature extraction, Headphones, user authentication, earphones, Energy consumption, head motion, Motion segmentation, System performance, ubiquitous computing, Ubiquitous computing},
+ pages = {1283--1293},
+ annote = {“users wear earphones while the system plays a random music segment. As the users perform head motions in response to the music, the terminal application initiates data collection. This process involves capturing two types of sensor data generated by the user: accelerometer data and gyroscope data” (Xie et al., 2024, p. 1286)
+},
+ file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\39FYYG69\\Xie et al. - 2024 - EarPass Unlock When Wearing Your Earphones.pdf:application/pdf},
+}</t>
+  </si>
+  <si>
+    <t>@article{xie_user_2024,
+ title = {User {Authentication} on {Earable} {Devices} via {Bone}-{Conducted} {Occlusion} {Sounds}},
+ volume = {21},
+ issn = {1941-0018},
+ url = {https://ieeexplore.ieee.org/document/10330729},
+ doi = {10.1109/TDSC.2023.3335368},
+ abstract = {With the rapid development of mobile devices and the fast increase of sensitive data, secure and convenient mobile authentication technologies are desired. Except for traditional passwords, many mobile devices have biometric-based authentication methods (e.g., fingerprint, voiceprint, and face recognition), but they are vulnerable to spoofing attacks. To solve this problem, we study new biometric features which are based on the dental occlusion and find that the bone-conducted sound of dental occlusion collected in binaural canals contains unique features of individual bones and teeth. Motivated by this, we propose a novel authentication system, TeethPass⁺+, which uses earbuds to collect occlusal sounds in binaural canals to achieve authentication. First, we design an event detection method based on spectrum variance to detect bone-conducted sounds. Then, we analyze the time-frequency domain of the sounds to filter out motion noises and extract unique features of users from four aspects: teeth structure, bone structure, occlusal location, and occlusal sound. Finally, we train a Triplet network to construct the user template, which is used to complete authentication. Through extensive experiments including 53 volunteers, the performance of TeethPass⁺+ in different environments is verified. TeethPass⁺+ achieves an accuracy of 98.6\% and resists 99.7\% of spoofing attacks.},
+ number = {4},
+ urldate = {2025-11-28},
+ journal = {IEEE Transactions on Dependable and Secure Computing},
+ author = {Xie, Yadong and Li, Fan and Wu, Yue and Wang, Yu},
+ month = jul,
+ year = {2024},
+ keywords = {Ear, Irrigation, Authentication, biometrics, Feature extraction, Biometrics (access control), acoustic sensing, Dentistry, Mobile authentication, occlusal sound, Teeth},
+ pages = {3704--3718},
+ annote = {“uses inward-facing microphones in earbuds to collect boneconducted sounds of dental occlusion in binaural canals to achieve authentication” (Xie et al., 2024, p. 3717)
+},
+ file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\23ZR7L7G\\Xie et al. - 2024 - User Authentication on Earable Devices via Bone-Conducted Occlusion Sounds.pdf:application/pdf},
+}</t>
+  </si>
+  <si>
+    <t>@article{wang_earslide_2024,
+ title = {{EarSlide}: a {Secure} {Ear} {Wearables} {Biometric} {Authentication} {Based} on {Acoustic} {Fingerprint}},
+ volume = {8},
+ shorttitle = {{EarSlide}},
+ url = {https://dl.acm.org/doi/10.1145/3643515},
+ doi = {10.1145/3643515},
+ abstract = {Ear wearables (earables) are emerging platforms that are broadly adopted in various applications. There is an increasing demand for robust earables authentication because of the growing amount of sensitive information and the IoT devices that the earable could access. Traditional authentication methods become less feasible due to the limited input interface of earables. Nevertheless, the rich head-related sensing capabilities of earables can be exploited to capture human biometrics. In this paper, we propose EarSlide, an earable biometric authentication system utilizing the advanced sensing capacities of earables and the distinctive features of acoustic fingerprints when users slide their fingers on the face. It utilizes the inward-facing microphone of the earables and the face-ear channel of the ear canal to reliably capture the acoustic fingerprint. In particular, we study the theory of friction sound and categorize the characteristics of the acoustic fingerprints into three representative classes, pattern-class, ridge-groove-class, and coupling-class. Different from traditional fingerprint authentication only utilizes 2D patterns, we incorporate the 3D information in acoustic fingerprint and indirectly sense the fingerprint for authentication. We then design representative sliding gestures that carry rich information about the acoustic fingerprint while being easy to perform. It then extracts multi-class acoustic fingerprint features to reflect the inherent acoustic fingerprint characteristic for authentication. We also adopt an adaptable authentication model and a user behavior mitigation strategy to effectively authenticate legit users from adversaries. The key advantages of EarSlide are that it is resistant to spoofing attacks and its wide acceptability. Our evaluation of EarSlide in diverse real-world environments with intervals over one year shows that EarSlide achieves an average balanced accuracy rate of 98.37\% with only one sliding gesture.},
+ number = {1},
+ urldate = {2025-11-26},
+ journal = {Proc. ACM Interact. Mob. Wearable Ubiquitous Technol.},
+ author = {Wang, Zi and Wang, Yilin and Yang, Jie},
+ year = {2024},
+ pages = {24:1--24:29},
+ annote = {“We capture representive features from pattern-class, ridge-groove-class, and coupling-class to extract 2D patterns, 3D ridgegroove, and coupling information of finger-face sliding interaction. We adopt of a Siamese neural network for adaptable authentication model and a strategy for user behavior mitigation to enhance our system’s performance.” (Wang et al., 2024, p. 27)
+},
+ file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\TRUM5CIM\\Wang et al. - 2024 - EarSlide a Secure Ear Wearables Biometric Authentication Based on Acoustic Fingerprint.pdf:application/pdf},
+}</t>
+  </si>
+  <si>
+    <t>@article{wang_budsauth_2024,
+ title = {{BudsAuth}: {Toward} {Gesture}-{Wise} {Continuous} {User} {Authentication} {Through} {Earbuds} {Vibration} {Sensing}},
+ volume = {11},
+ issn = {2327-4662},
+ shorttitle = {{BudsAuth}},
+ url = {https://ieeexplore.ieee.org/document/10478100},
+ doi = {10.1109/JIOT.2024.3380811},
+ abstract = {The surge in popularity of wireless headphones, particularly wireless earbuds, as smart wearables, has been notable in recent years. These devices, empowered by artificial intelligence (AI), are broadening their utility in areas such as speech recognition, augmented reality, pose recognition, and health care monitoring, thereby enriching user experiences through novel interactive interfaces driven by embedded sensors. However, the widespread adoption of wireless earbuds has spurred concerns regarding security and privacy, necessitating robust bespoke security measures. Despite the miniaturization of mobile chips enabling the integration of sophisticated algorithms into smart wearables, the research and industrial communities have yet to accord adequate attention to earbud security. This article focuses on empowering wireless earbuds to authenticate their legitimate users, tackling the challenges associated with conventional authentication methods. Instead of relying on input interface authentication methods like PIN or lock patterns, this research delves into leveraging inertial measurement unit (IMU) data collected during interactions with devices to extract novel biometric features, presenting an alternative approach that nonetheless confronts challenges related to signal capture and interference. Consequently, we propose and design BudsAuth, an implicit user authentication framework that harnesses built-in IMU sensors in smart earbuds to capture vibration signals induced by on-face touching interactions with the earbuds. These vibrations are utilized to deliver continuous and implicit user authentication with high precision and compatibility across various earbud models. Extensive evaluation demonstrates BudsAuth’s capability to achieve an equal error rate (EER) of 0.0003, representing an approximate 99.97\% accuracy with seven consecutive samples of interactive gestures for implicit authentication.},
+ number = {12},
+ urldate = {2025-11-27},
+ journal = {IEEE Internet of Things Journal},
+ author = {Wang, Yong and Yang, Tianyu and Wang, Chunxiao and Li, Feng and Hu, Pengfei and Shen, Yiran},
+ month = jun,
+ year = {2024},
+ keywords = {Authentication, Sensors, Wearable devices, Adversarial learning, Communication system security, implicit authentication, Security, wearable computing, Wireless communication, Wireless sensor networks},
+ pages = {22007--22020},
+ annote = {“In the authentication phase, BudsAuth receives new vibration signals generated by an on-skin gesture. It extracts features using the personalized feature encoder obtained from the registration phase. BudsAuth performs implicit user authentication and spoofer detection by comparing the extracted features with the templates of the registered user. Finally, a weighted voting method is adopted to fuse the results from multiple consecutive on-skin gestures to achieve highprecision implicit authentication.” (Wang et al., 2024, p. 22010)
+},
+ file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\RW99TCPR\\Wang et al. - 2024 - BudsAuth Toward Gesture-Wise Continuous User Authentication Through Earbuds Vibration Sensing.pdf:application/pdf},
+}</t>
+  </si>
+  <si>
+    <t>@inproceedings{srivastava_jawthenticate_2024,
+ address = {New York, NY, USA},
+ series = {{SenSys} '23},
+ title = {Jawthenticate: {Microphone}-free {Speech}-based {Authentication} using {Jaw} {Motion} and {Facial} {Vibrations}},
+ isbn = {979-8-4007-0414-7},
+ shorttitle = {Jawthenticate},
+ url = {https://dl.acm.org/doi/10.1145/3625687.3625813},
+ doi = {10.1145/3625687.3625813},
+ abstract = {In this paper, we present Jawthenticate, an earable system that authenticates a user using audible or inaudible speech without using a microphone. This system can overcome the shortcomings of traditional voice-based authentication systems like unreliability in noisy conditions and spoofing using microphone-based replay attacks. Jawthenticate derives distinctive speech-related features from the jaw motion and associated facial vibrations. This combination of features makes Jawthenticate resilient to vocal imitations as well as camera-based spoofing. We use these features to train a two-class SVM classifier for each user. Our system is invariant to the content and language of speech. In a study conducted with 41 subjects, who speak different native languages, Jawthenticate achieves a Balanced Accuracy (BAC) of 97.07\%, True Positive Rate (TPR) of 97.75\%, and True Negative Rate (TNR) of 96.4\% with just 3 seconds of speech data.},
+ urldate = {2025-11-26},
+ booktitle = {Proceedings of the 21st {ACM} {Conference} on {Embedded} {Networked} {Sensor} {Systems}},
+ publisher = {Association for Computing Machinery},
+ author = {Srivastava, Tanmay and Pan, Shijia and Nguyen, Phuc and Jain, Shubham},
+ year = {2024},
+ pages = {209--222},
+ file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\U35K293W\\Srivastava et al. - 2024 - Jawthenticate Microphone-free Speech-based Authentication using Jaw Motion and Facial Vibrations.pdf:application/pdf},
+}</t>
+  </si>
+  <si>
+    <t>@inproceedings{mizuho_earauthcam_2024,
+ address = {New York, NY, USA},
+ series = {{AHs} '24},
+ title = {{EarAuthCam}: {Personal} {Identification} and {Authentication} {Method} {Using} {Ear} {Images} {Acquired} with a {Camera}-{Equipped} {Hearable} {Device}},
+ isbn = {979-8-4007-0980-7},
+ shorttitle = {{EarAuthCam}},
+ url = {https://dl.acm.org/doi/10.1145/3652920.3653059},
+ doi = {10.1145/3652920.3653059},
+ abstract = {Earphones are now used for longer hours than before with the advancement in wireless technology and miniaturization. In addition, the application of earphones has become more diverse, and opportunities to access highly confidential information through them have increased. We propose a method comprising a hearable device equipped with a small camera for user authentication from ear images. This method improves the security of the hearable device. Ear images are first captured with the camera. The ear regions in the images are then extracted using a mask region-based convolutional neural network. Finally, the user is identified using histograms of oriented gradient features and a support vector machine (SVM). Our method was able to identify 18 participants with an accuracy of 84.1\%. Users are authenticated through unsupervised anomaly detection using an autoencoder with an error rate of 8.36\%. This method facilitates hands- and eye-free operations without requiring any explicit authentication action by the user.},
+ urldate = {2025-11-26},
+ booktitle = {Proceedings of the {Augmented} {Humans} {International} {Conference} 2024},
+ publisher = {Association for Computing Machinery},
+ author = {Mizuho, Yurina and Kawasaki, Yohei and Amesaka, Takashi and Sugiura, Yuta},
+ year = {2024},
+ pages = {119--130},
+ file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\TC7SFSQA\\Mizuho et al. - 2024 - EarAuthCam Personal Identification and Authentication Method Using Ear Images Acquired with a Camer.pdf:application/pdf},
+}</t>
+  </si>
+  <si>
+    <t>@article{hu_lr-auth_2024,
+ title = {{LR}-{Auth}: {Towards} {Practical} {Implementation} of {Implicit} {User} {Authentication} on {Earbuds}},
+ volume = {8},
+ shorttitle = {{LR}-{Auth}},
+ url = {https://dl.acm.org/doi/10.1145/3699793},
+ doi = {10.1145/3699793},
+ abstract = {The increasing use of earbuds in applications like immersive entertainment and health monitoring necessitates effective implicit user authentication systems to preserve the privacy of sensitive data and provide personalized experiences. Existing approaches, which leverage physiological cues (e.g., jawbone structure) and behavioral cues (e.g., gait), face challenges such as limited usability, high delay and energy overhead, and significant computational demands, rendering them impractical for resource-constrained earbuds. To address these issues, we present LR-Auth, a lightweight, user-friendly implicit authentication system designed for various earbud usage scenarios. LR-Auth utilizes the modulation of sound frequencies by the user's unique occluded ear canal, generating user-specific templates through linear correlations between two audio streams instead of complex machine-learning models. Our prototype, evaluated with 30 subjects under diverse conditions, demonstrates over 99\% balanced accuracy with five 100 ms audio segments, even in noisy environments and during music playback. LR-Auth significantly reduces system overhead, achieving a 20 × to 404 × decrease in latency and a 24 × to 410 × decrease in energy consumption compared to existing methods. These results highlight LR-Auth's potential for accurate, robust, and efficient user authentication on resource-constrained earbuds.},
+ number = {4},
+ urldate = {2025-11-27},
+ journal = {Proc. ACM Interact. Mob. Wearable Ubiquitous Technol.},
+ author = {Hu, Changshuo and Ma, Xiao and Huang, Xinger and Shen, Yiran and Ma, Dong},
+ year = {2024},
+ pages = {155:1--155:27},
+ file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\Z82UNBI2\\Hu et al. - 2024 - LR-Auth Towards Practical Implementation of Implicit User Authentication on Earbuds.pdf:application/pdf},
+}</t>
+  </si>
+  <si>
+    <t>@article{he_hcr-auth_2024,
+ title = {{HCR}-{Auth}: {Reliable} {Bone} {Conduction} {Earphone} {Authentication} with {Head} {Contact} {Response}},
+ volume = {8},
+ shorttitle = {{HCR}-{Auth}},
+ url = {https://dl.acm.org/doi/10.1145/3699780},
+ doi = {10.1145/3699780},
+ abstract = {Earables, or ear wearables, are increasingly being used for a variety of personal applications, prompting the development of authentication schemes to safeguard user privacy. Existing authentications are designed for traditional in-ear earphones, relying on a closed ear canal environment, which is not suited for bone conduction earphones that feature an open-ear design. In this paper, we propose HCR-Auth, a new authentication approach for bone conduction earphones based on head biometrics. It employs a modulated chirp signal, emitted by the earphone speaker, to actively sense the user's head structure, and captures the response through the earphone's accelerometer. It operates implicitly, eliminating additional efforts from the user to perform authentication. Through extensive experiments involving 60 subjects, we determine that HCR-Auth achieves a commendable balanced accuracy of 96.55\% using only 10 registration samples, proving its efficacy and resilience against potential threats. Our dataset and source codes are available at https://anonymous.4open.science/r/HCR-Auth-D43B/.},
+ number = {4},
+ urldate = {2025-11-27},
+ journal = {Proc. ACM Interact. Mob. Wearable Ubiquitous Technol.},
+ author = {He, Zhixiang and Chen, Jing and Wu, Cong and He, Kun and Du, Ruiying and Jia, Ju and Gu, Yangyang and Sun, Xiping},
+ year = {2024},
+ pages = {208:1--208:27},
+ file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\E28CBSNV\\He et al. - 2024 - HCR-Auth Reliable Bone Conduction Earphone Authentication with Head Contact Response.pdf:application/pdf},
+}</t>
+  </si>
+  <si>
+    <t>@article{han_exploring_2024,
+ title = {Exploring {Earable}-{Based} {Passive} {User} {Authentication} via {Interpretable} {In}-{Ear} {Breathing} {Biometrics}},
+ volume = {23},
+ issn = {1558-0660},
+ url = {https://ieeexplore.ieee.org/abstract/document/10663927},
+ doi = {10.1109/TMC.2024.3453412},
+ abstract = {As earable devices have become indispensable smart devices in people's lives, earable-based user authentication has gradually attracted widespread attention. In our work, we explore novel in-ear breathing biometrics and design an earable-based authentication approach, named BreathSign, which takes advantage of inward-facing microphones on commercial earphones to capture in-ear breathing sounds for passive authentication. To expand the differences among individuals, we model the process of breathing sound generation, transmission, and reception. Based on that, we derive hard-to-forge physical-level features from in-ear breathing sounds as biometrics. Furthermore, to eliminate the impact of breathing behavioral patterns (e.g., duration and intensity), we design a triple network model to extract breathing behavior-independent features and design an online user template update mechanism for long-term authentication. Extensive experiments with 35 healthy subjects have been conducted to evaluate the performance of BreathSign. The results show that our system achieves the average authentication accuracy of 93.15\%, 98.06\%, and 99.74\% via one, five, and nine breathing cycles, respectively. Regarding the resistance of spoofing attacks, BreathSign could achieve an average EER of approximately 3.5\%. Compared with other behavior-based authentication schemes, BreathSign does not require users to perform complex movements or postures but only effortless breathing for authentication and can be easily implemented on commercial earphones with high usability and enhanced security.},
+ number = {12},
+ urldate = {2025-11-27},
+ journal = {IEEE Transactions on Mobile Computing},
+ author = {Han, Feiyu and Yang, Panlong and Feng, Yuanhao and Du, Haohua and Li, Xiang-Yang},
  month = dec,
- year = {2016},
- keywords = {Ear, Headphones, Microphones, Acoustics, Acoustic, Atmospheric measurements, Ear Recognition, Frequency measurement, Particle measurements},
- pages = {1--4},
- file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\CPG8SP97\\Derawi - 2016 - Biometric acoustic ear recognition.pdf:application/pdf},
-}</t>
-  </si>
-  <si>
-    <t>@inproceedings{curran_passthoughts_2016,
- title = {Passthoughts authentication with low cost {EarEEG}},
- issn = {1558-4615},
- url = {https://ieeexplore.ieee.org/document/7591112},
- doi = {10.1109/EMBC.2016.7591112},
- abstract = {Personal and wearable computing are moving toward smaller and more seamless devices. We explore how this trend could be mirrored in an authentication scheme based on electroencephalography (EEG) signals collected from the ear. We evaluate this model using a low cost, single-channel, consumer grade device for data collection. Using data from 12 study participants who performed a set of 5 mental tasks, we achieve a 44\% reduction in half total error rate (HTER) compared with a random classifier, corresponding to a 72\% authentication accuracy in within-participants analyses and a 60\% reduction and 80\% accuracy in between-participant analyses. Given our results and those of previous research, we conclude that earEEG shows potential as a uniquely convenient authentication method as it is integrable into devices like earbud headphones already commonly worn in the ear, and the mental gestures generating the signal are invisible to would-be eavesdroppers.},
- urldate = {2026-01-16},
- booktitle = {2016 38th {Annual} {International} {Conference} of the {IEEE} {Engineering} in {Medicine} and {Biology} {Society} ({EMBC})},
- author = {Curran, Max T. and Yang, Jong-kai and Merrill, Nick and Chuang, John},
- month = aug,
- year = {2016},
- note = {ISSN: 1558-4615},
- keywords = {Ear, Authentication, Electroencephalography, Sensors, Electrodes, Face, Testing},
- pages = {1979--1982},
- file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\MNK9IM44\\Curran et al. - 2016 - Passthoughts authentication with low cost EarEEG.pdf:application/pdf},
-}</t>
-  </si>
-  <si>
-    <t>@inproceedings{curran_one-step_2017,
+ year = {2024},
+ keywords = {Ear, Irrigation, Authentication, Feature extraction, Biometrics, Headphones, Microphones, Breathing biometrics, earable sensing, in-ear breathing sounds, passive authentication},
+ pages = {15238--15255},
+ file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\MNV4XV7B\\Han et al. - 2024 - Exploring Earable-Based Passive User Authentication via Interpretable In-Ear Breathing Biometrics.pdf:application/pdf},
+}</t>
+  </si>
+  <si>
+    <t>@inproceedings{duan_f2key_2024,
  address = {New York, NY, USA},
- series = {{UbiComp} '17},
- title = {One-step, three-factor authentication in a single earpiece},
- isbn = {978-1-4503-5190-4},
- url = {https://dl.acm.org/doi/10.1145/3123024.3123087},
- doi = {10.1145/3123024.3123087},
- abstract = {Multifactor authentication presents a robust security method, but typically requires multiple steps on the part of the user resulting in a high cost to usability and limiting adoption. Furthermore, a truly usable system must be unobtrusive and inconspicuous. Here, we present a system that provides all three factors of authentication (knowledge, possession, and inherence) in a single step in the form of an earpiece which implements brain-based authentication via custom-fit, in-ear electroencephalography (EEG). We demonstrate its potential by collecting EEG data using manufactured custom-fit earpieces with embedded electrodes. Across 7 participants, we are able to achieve perfect performance, mean 0\% false acceptance (FAR) and 0\% false rejection rates (FRR), using participants' best performing tasks collected in one session by one earpiece with three electrodes. Our results indicate that a single earpiece with embedded electrodes could provide a discreet, convenient, and robust method for secure one-step, three-factor authentication.},
- urldate = {2026-01-16},
- booktitle = {Proceedings of the 2017 {ACM} {International} {Joint} {Conference} on {Pervasive} and {Ubiquitous} {Computing} and {Proceedings} of the 2017 {ACM} {International} {Symposium} on {Wearable} {Computers}},
+ series = {{MOBISYS} '24},
+ title = {{F2Key}: {Dynamically} {Converting} {Your} {Face} into a {Private} {Key} {Based} on {COTS} {Headphones} for {Reliable} {Voice} {Interaction}},
+ isbn = {979-8-4007-0581-6},
+ shorttitle = {{F2Key}},
+ url = {https://dl.acm.org/doi/10.1145/3643832.3661860},
+ doi = {10.1145/3643832.3661860},
+ abstract = {In this paper, we proposed F2Key, the first earable physical security system based on commercial off-the-shelf headphones. F2Key enables impactful applications, such as enhancing voiceprint-based authentication systems, reliable voice assistants, audio deepfake defense, and the legal validity of artifacts. The key idea of F2Key is to establish a stable acoustic sensing field across the user's face and embed the user's facial structures and articulatory habits into a user-specific generative model that serves as a private key. The private key can decrypt the Channel Impulse Response (CIR) profiles provided by the acoustic sensing field into an inferred spectrogram that can match the real one calculated from the corresponding speech, provided that the user's CIR-spectrogram mapping relationship is consistent with the one embedded in the generative model. Extensive experiments demonstrate that F2Key resists 99.9\%, 96.4\%, and 95.3\% of speech replay attacks, mimicry attacks, and hybrid attacks, respectively. We discussed and evaluated F2Key from different perspectives, such as the health consideration and identical twins study, to show the practicality and reliability.},
+ urldate = {2025-11-26},
+ booktitle = {Proceedings of the 22nd {Annual} {International} {Conference} on {Mobile} {Systems}, {Applications} and {Services}},
  publisher = {Association for Computing Machinery},
- author = {Curran, Max T. and Merrill, Nick and Chuang, John and Gandhi, Swapan},
- year = {2017},
- pages = {21--24},
- file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\7FT9XIRU\\Curran et al. - 2017 - One-step, three-factor authentication in a single earpiece.pdf:application/pdf},
-}</t>
-  </si>
-  <si>
-    <t>@inproceedings{clarke_motion_2020,
- address = {New York, NY, USA},
- series = {{MUM} '20},
- title = {Motion {Coupling} of {Earable} {Devices} in {Camera} {View}},
- isbn = {978-1-4503-8870-2},
- url = {https://dl.acm.org/doi/10.1145/3428361.3428470},
- doi = {10.1145/3428361.3428470},
- abstract = {Earables, earphones augmented with inertial sensors and real-time data accessibility, provide the opportunity for private audio channels in public settings. One of the main challenges of achieving this goal is to correctly associate which device belongs to which user without prior information. In this paper, we explore how motion of an earable, as measured by the on-board accelerometer, can be correlated against detected faces from a webcam to accurately match which user is wearing the device. We conduct a data collection and explore which type of user movement can be accurately detected using this approach, and investigate how varying the speed of the movement affects detection rates. Our results show that the approach achieves greater detection results for faster movements, and that it can differentiate the same movement across different participants with a detection rate of 86\%, increasing to 92\% when differentiating a movement against others.},
- urldate = {2026-01-17},
- booktitle = {Proceedings of the 19th {International} {Conference} on {Mobile} and {Ubiquitous} {Multimedia}},
- publisher = {Association for Computing Machinery},
- author = {Clarke, Christopher and Ehrich, Peter and Gellersen, Hans},
- year = {2020},
- pages = {13--17},
- file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\LKE6Y3Y4\\Clarke et al. - 2020 - Motion Coupling of Earable Devices in Camera View.pdf:application/pdf},
-}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@inproceedings{arakawa_fast_2016,
- title = {Fast and accurate personal authentication using ear acoustics},
- url = {https://ieeexplore.ieee.org/document/7820886},
- doi = {10.1109/APSIPA.2016.7820886},
- abstract = {This paper presents a biometric personal-authentication method that exploits acoustic characteristics of human ears. It transmits a probe signal into the ear and receives its reflection, which contains personal identity information about the shape of the ear canal. Based on a study of effective and efficient acoustic feature representation and the use of audio equipment suitable for acquiring features with low within-individual variability, the proposed method achieves a promising equal error rate of 0.97\% with only 12 feature components. A prototype system for Android smartphones is also presented.},
- urldate = {2026-01-16},
- booktitle = {2016 {Asia}-{Pacific} {Signal} and {Information} {Processing} {Association} {Annual} {Summit} and {Conference} ({APSIPA})},
- author = {Arakawa, Takayuki and Koshinaka, Takafumi and Yano, Shohei and Irisawa, Hideki and Miyahara, Ryoji and Imaoka, Hitoshi},
- month = dec,
- year = {2016},
- keywords = {Ear, Irrigation, Authentication, Headphones, Smart phones, Mel frequency cepstral coefficient},
- pages = {1--4},
- file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\IC66LC5V\\Arakawa et al. - 2016 - Fast and accurate personal authentication using ear acoustics.pdf:application/pdf},
-}
-</t>
-  </si>
-  <si>
-    <t>@inproceedings{akkermans_acoustic_2005,
- title = {Acoustic ear recognition for person identification},
- url = {https://ieeexplore.ieee.org/document/1544428},
- doi = {10.1109/AUTOID.2005.11},
- abstract = {In this paper we investigate how the acoustic properties of the pinna-i.e., the outer flap of the ear- and the ear canal can be used as a biometric. The acoustic properties can be measured relatively easy with an inexpensive sensor and feature vectors can be derived with little effort. We achieve equal error rates in the order of 1.5\%-7\%, depending on the application device that is used to do the measurement.},
- urldate = {2026-01-16},
- booktitle = {Fourth {IEEE} {Workshop} on {Automatic} {Identification} {Advanced} {Technologies} ({AutoID}'05)},
- author = {Akkermans, A.H.M. and Kevenaar, T.A.M. and Schobben, D.W.E.},
- month = oct,
- year = {2005},
- keywords = {Ear, Irrigation, Acoustic devices, Acoustic measurements, Biometrics, Fingerprint recognition, Loudspeakers, Resonance, Shape, Transfer functions},
- pages = {219--223},
- file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\JFCZWR75\\Akkermans et al. - 2005 - Acoustic ear recognition for person identification.pdf:application/pdf},
+ author = {Duan, Di and Sun, Zehua and Ni, Tao and Li, Shuaicheng and Jia, Xiaohua and Xu, Weitao and Li, Tianxing},
+ year = {2024},
+ pages = {127--140},
+ file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\93ZRMKYL\\Duan et al. - 2024 - F2Key Dynamically Converting Your Face into a Private Key Based on COTS Headphones for Reliable Voi.pdf:application/pdf},
+}</t>
+  </si>
+  <si>
+    <t>@inproceedings{zhou_baroauth_2025,
+ title = {{BaroAuth}: {Harnessing} {Ear} {Canal} {Deformation} for {Speaking} {User} {Authentication} on {Earbuds}},
+ shorttitle = {{BaroAuth}},
+ url = {https://ieeexplore.ieee.org/document/11183763},
+ doi = {10.1109/ICDCS63083.2025.00020},
+ abstract = {The growing adoption of smart wearable devices (e.g., earbuds and smart watches) poses new challenges for secure and seamless user authentication due to their limited interaction interfaces. Conventional biometric methods, including fingerprints, voice, and facial recognition, often suffer from usability constraints, noise interference, or susceptibility to spoofing attacks. In this paper, we propose BaroAuth, a novel authentication system that utilizes the stable and distinctive patterns of Speech-aware Pressure Sequences (SPSs) captured by miniature MEMS barometers embedded in earbuds. The design of BaroAuth is based on two key observations. First, speech production involves coordinated movements of articulatory organs, such as the jaw, tongue, and soft palate, which reshape the ear canal geometry via the temporomandibular joint (TMJ), generating subtle pressure variations that encode the speaker’s unique articulatory dynamics and physiological traits. Second, SPSs demonstrate strong intra-individual consistency and notable inter-individual variability, which can be effectively captured by barometers. We implement the prototype of BaroAuth and conduct comprehensive experiments on it. Experimental results demonstrate that BaroAuth achieves a mean false-acceptance rate (FAR) and false-rejection rate (FRR) of 1.62\% and 1.74\%, respectively, even under sophisticated attack scenarios.},
+ urldate = {2025-11-28},
+ booktitle = {2025 {IEEE} 45th {International} {Conference} on {Distributed} {Computing} {Systems} ({ICDCS})},
+ author = {Zhou, Luo and Chang, Shan and Luo, Jiusong and Wen, Huixiang and Zhu, Hongzi and Lu, Li},
+ month = jul,
+ year = {2025},
+ note = {ISSN: 2575-8411},
+ keywords = {Ear, Irrigation, Authentication, Feature extraction, Wearable devices, Physiology, barometer, Barometers, Deformation, ear canal deformation, earbuds, Microelectromechanical systems, speaking user authentication, Working environment noise},
+ pages = {111--121},
+ annote = {“pressure signals from the left and right ear canals precede audio signals recorded by a microphone” (Zhou et al., 2025, p. 113)
+},
+ file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\H9B6X578\\Zhou et al. - 2025 - BaroAuth Harnessing Ear Canal Deformation for Speaking User Authentication on Earbuds.pdf:application/pdf},
+}</t>
+  </si>
+  <si>
+    <t>@article{wu_3d_2025,
+ title = {{3D} {Facial} {Tracking} and {User} {Authentication} {Through} {Lightweight} {Single}-{Ear} {Biosensors}},
+ volume = {24},
+ issn = {1558-0660},
+ url = {https://ieeexplore.ieee.org/abstract/document/10701549},
+ doi = {10.1109/TMC.2024.3470339},
+ abstract = {Facial landmark tracking and 3D reconstruction have gained considerable attention due to their numerous applications such as human-computer interactions, facial expression analysis, and emotion recognition, etc. Traditional approaches require users to be confined to a particular location and face a camera under constrained recording conditions, which prevents them from being deployed in many application scenarios involving human motions. In this paper, we propose the first single-earpiece lightweight biosensing system, BioFace-3D, that can unobtrusively, continuously, and reliably sense the entire facial movements, track 2D facial landmarks, and further render 3D facial animations. Our single-earpiece biosensing system takes advantage of the cross-modal transfer learning model to transfer the knowledge embodied in a high-grade visual facial landmark detection model to the low-grade biosignal domain. After training, our BioFace-3D can directly perform continuous 3D facial reconstruction from the biosignals, without any visual input. Additionally, by utilizing biosensors, we also showcase the potential for capturing both behavioral aspects, such as facial gestures, and distinctive individual physiological traits, establishing a comprehensive two-factor authentication/identification framework. Extensive experiments involving 16 participants demonstrate that BioFace-3D can accurately track 53 major facial landmarks with only 1.85 mm average error and 3.38\% normalized mean error, which is comparable with most state-of-the-art camera-based solutions. Experiments also show that the system can authenticate users with high accuracy (e.g., over 99.8\% within two trials for three gestures in series), low false positive rate (e.g., less 0.24\%), and is robust to various types of attacks.},
+ number = {2},
+ urldate = {2025-11-28},
+ journal = {IEEE Transactions on Mobile Computing},
+ author = {Wu, Yi and Zhang, Xiande and Wu, Tianhao and Zhou, Bing and Nguyen, Phuc and Liu, Jian},
+ month = feb,
+ year = {2025},
+ keywords = {Authentication, Training, user authentication, Sensors, Biological system modeling, Visualization, Mobile computing, 3D facial reconstruction, Biosensors, Facial animation, single-ear biosensing, Solid modeling, Three-dimensional displays, Tracking, wearable sensing},
+ pages = {749--762},
+ annote = {“BioFace-3D is the first single-earpiece biosensing system that can unobtrusively, continuously, and reliably sense the entire facial movements, track 2D facial landmarks, and further render 3D facial animations through fitting a 3D head model to the 2D facial landmarks.” (Wu et al., 2025, p. 750)
+},
+ file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\UVLHPV5B\\Wu et al. - 2025 - 3D Facial Tracking and User Authentication Through Lightweight Single-Ear Biosensors.pdf:application/pdf},
+}</t>
+  </si>
+  <si>
+    <t>@article{liu_decoding_2025,
+ title = {Decoding {Air} {Friction} {Rhythms}: {Enabling} {User} {Identification} with {Out}-{Ear} {Microphones} in {COTS} {Earphones}},
+ issn = {1558-0660},
+ shorttitle = {Decoding {Air} {Friction} {Rhythms}},
+ url = {https://ieeexplore.ieee.org/document/11219195},
+ doi = {10.1109/TMC.2025.3626359},
+ abstract = {Ear-worn devices (earables) are increasingly central to smart system interactions involving privacy-sensitive data, yet secure user authentication on these devices remains a challenge. Existing methods often depend on auxiliary sensors like in-ear microphones or accelerometers, which are absent in many commercial earables. This paper introduces a novel biometric approach leveraging natural head gestures. We observe that head gestures generate unique air friction patterns detectable by out-ear microphones, producing sonic signatures shaped by the head and neck's musculoskeletal dynamics. These signatures serve as a robust basis for earable authentication. We propose HMPrint, a system that captures air-friction-induced sonic effects (AFiSe) from head gestures via outear microphones for authentication. HMPrint incorporates advanced spectral analysis, synthetic data generation using variational autoencoders, and a contrastive continual learning framework to enhance robustness against inconsistent wearing postures, varied movement patterns, and environmental noise. A proof-of-concept prototype was tested with 30 participants and 15 commercial earable models across diverse conditions. Results show that HMPrint achieves high authentication accuracy (97.49\% recall), a low FAR (2.34\%), and strong resistance to spoofing (98\% success rate).},
+ urldate = {2025-11-28},
+ journal = {IEEE Transactions on Mobile Computing},
+ author = {Liu, Daibo and Lu, Hang and Qi, Xiaomeng and Rong, Huigui and Chen, Haowen and Jiang, Hongbo},
+ year = {2025},
+ keywords = {Ear, Authentication, Biometrics, Transfer functions, Headphones, user authentication, Sensors, Microphones, Acoustics, Microelectromechanical systems, Mobile computing, earables, head gestures, Neck, out-ear micophones},
+ pages = {1--16},
+ file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\LSS2EJQV\\Liu et al. - 2025 - Decoding Air Friction Rhythms Enabling User Identification with Out-Ear Microphones in COTS Earphon.pdf:application/pdf},
+}</t>
+  </si>
+  <si>
+    <t>@article{huang_eve_2025,
+ title = {Eve {Said} {Yes}: {AirBone} {Authentication} for {Head}-{Wearable} {Smart} {Voice} {Assistant}},
+ volume = {24},
+ issn = {1558-0660},
+ shorttitle = {Eve {Said} {Yes}},
+ url = {https://ieeexplore.ieee.org/document/10947223},
+ doi = {10.1109/TMC.2025.3530962},
+ abstract = {Recent advances in speech and language processing have led to the rise of smart voice services like Alexa, Google Home, and Siri. However, these advancements also increase security risks due to sophisticated voice domain attacks. Instead of relying on acoustic clues to detect replayed or synthesized speech, we utilize microphones and motion sensors in head-wearable devices to authorize legitimate users through bone-conducted vibrations, enabling multi-factor authentication (MFA) for spoken voice. Our proposed two-stage authentication system, AirBone, captures air and bone conduction (AirBone) signals and exploits two authentication factors sequentially. The first stage, called temporal consistency scoring (TCS), employs signal processing to verify the recorded AC and BC signals are concurrent and originate from the same vocalization process. Statistical tools are employed to distinguish legitimate attempts against false-triggering or acoustic attacks. The second stage leverages deep learning to verify the user’s unique bone conduction patterns in the vibration domain. Specifically, we enhance the robustness through data augmentation with constant-Q transform and adversarial training, improving the model’s ability to detect impersonation and machine-induced vibrations. Thanks to these designs, AirBone authentication offers enhanced security via MFA with no extra cost of user effort. In addition, our experimental results demonstrate a 96.3\%96.3\% overall accuracy, robustness against AirBone noise and room impulse responses, and 0.3\%0.3\% Equal Error Rate (EER) against acoustic and cross-domain attacks.},
+ number = {9},
+ urldate = {2025-11-28},
+ journal = {IEEE Transactions on Mobile Computing},
+ author = {Huang, Chenpei and Zhong, Hui and Prakash, Pavana and Shi, Dian and Yuan, Xu and Pan, Miao},
+ month = sep,
+ year = {2025},
+ keywords = {Ear, Authentication, Training, Vibrations, Security, User authentication, Acoustics, Bones, metaverse, Motion detection, multi-factor authentication, security and privacy, Solids, Spectrogram},
+ pages = {7836--7850},
+ file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\M8LGLQ2E\\Huang et al. - 2025 - Eve Said Yes AirBone Authentication for Head-Wearable Smart Voice Assistant.pdf:application/pdf},
+}</t>
+  </si>
+  <si>
+    <t>@article{he_headsonic_2025,
+ title = {{HeadSonic}: {Usable} {Bone} {Conduction} {Earphone} {Authentication} via {Head}-{Conducted} {Sounds}},
+ volume = {24},
+ issn = {1558-0660},
+ shorttitle = {{HeadSonic}},
+ url = {https://ieeexplore.ieee.org/document/10925832},
+ doi = {10.1109/TMC.2025.3551272},
+ abstract = {Earables (ear wearables) are rapidly emerging as a new platform encompassing a diverse of personal applications, prompting the development of authentication schemes to protect user privacy. Existing earable authentication methods are all specifically designed for air-conduction earphones, which are not suited for bone conduction earphones (BCEs) that rely on bone conduction mechanisms. In this paper, we propose HeadSonic, a usable BCE authentication system based on the unique head-conducted sounds, which can be acquired when the user wears the BCE device. Specifically, the system emits a millisecond-level sound to initiate the authentication session. The signal captured by the BCE microphone is propagated through the user's head, which is unique in density, geometry, and bone-tissue ratio. It operates implicitly, while maintaining robustness across different behaviors. Extensive experiments involving 60 subjects demonstrate that HeadSonic achieves a commendable balanced accuracy of 96.59\%, proving its efficacy and resilience against replay and synthesis attacks. Our dataset and source codes are available at https://anonymous.4open.science/r/HeadSonic-1CE4.},
+ number = {9},
+ urldate = {2025-11-28},
+ journal = {IEEE Transactions on Mobile Computing},
+ author = {He, Zhixiang and Chen, Jing and He, Kun and Gu, Yangyang and Deng, Qiyi and Zhang, Zijian and Du, Ruiying and Zhao, Qingchuan and Wu, Cong},
+ month = sep,
+ year = {2025},
+ keywords = {Ear, Authentication, biometrics, Biometrics, Sensors, Microphones, Acoustics, Mobile computing, acoustic sensing, Geometry, Noise, Reflection, Wearable authentication},
+ pages = {7914--7928},
+ file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\F9ZX3AAE\\He et al. - 2025 - HeadSonic Usable Bone Conduction Earphone Authentication via Head-Conducted Sounds.pdf:application/pdf},
+}</t>
+  </si>
+  <si>
+    <t>@article{gao_quick-pass_2025,
+ title = {Quick-pass {Continuous} {Authentication} with {Real}-time {Biometrics} {Extraction} on {COTS} {Earphones} {Using} {Out}-ear {Microphones}},
+ issn = {1558-0660},
+ url = {https://ieeexplore.ieee.org/document/11153058},
+ doi = {10.1109/TMC.2025.3606846},
+ abstract = {Continuous authentication is increasingly critical for cyber security. However, existing approaches are time-consuming due to their simplistic signal modulation and low efficiency in feature extraction. In this paper, we propose a continuous authentication technique, OnePiece. OnePiece is free from the requirement of in-ear microphones, which are necessary for existing earphone authentication systems. It exploits out-ear microphones for biometrics extraction, which are ubiquitous on off-the-shelf earphones. We analyze the acoustic response model of ears towards out-ear microphones via the air, which is different from that towards in-ear microphones. A frequency-varying ultrasonic modulation scheme is proposed to characterize in-depth ear biometrics in user-friendly, error-free, and time-efficient ways. Therefore, OnePiece enables quick-pass authentication once users wear the earphones, followed by continuous authentication covering the whole course. Moreover, we propose a wake-up mechanism to reduce the consumed power, which addresses the key power consumption issue in ultrasonic sensing techniques. Particularly, OnePiece can be smoothly deployed on off-the-shelf wired and wireless earphones. It performs good cross-device performance in which users just register only once. Extensive evaluations are conducted to validate its effectiveness under real-world scenarios.},
+ urldate = {2025-11-28},
+ journal = {IEEE Transactions on Mobile Computing},
+ author = {Gao, Ming and Chen, Jiatong and Tong, Xin and Ye, Ruitong and Chen, Yike and Xiao, Fu and Han, Jinsong},
+ year = {2025},
+ keywords = {Ear, Authentication, Biometrics, Headphones, Internet of Things, Sen10.1145/3643832.3661860sors, Wireless sensor networks, Acoustic Sensing, Microphones, Acoustics, Continuous User Authentication, Earable Sensing, Ultrasonic imaging},
+ pages = {1--18},
+ file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\SRFMZJ7R\\Gao et al. - 2025 - Quick-pass Continuous Authentication with Real-time Biometrics Extraction on COTS Earphones Using Ou.pdf:application/pdf},
+}</t>
+  </si>
+  <si>
+    <t>@article{cao_enabling_2025,
+ title = {Enabling {Passive} {User} {Authentication} via {Heart} {Sounds} on {In}-{Ear} {Microphones}},
+ volume = {22},
+ issn = {1941-0018},
+ url = {https://ieeexplore.ieee.org/document/10604926},
+ doi = {10.1109/TDSC.2024.3429574},
+ abstract = {Biometrics has been increasingly integrated into wearables for enhanced data security in recent years. Meanwhile, wearable popularity offers a unique chance to capture novel biometrics via embedded sensors. In this article, we study new intracorporal biometrics combining the uniqueness of heart motion, bone conduction, and body asymmetry. Specifically, we introduce HeartPrint, a passive yet secure user authentication system exploiting the bone-conducted heart sounds captured by (widely available) dual in-ear microphones (IEMs). To eliminate interference, we devise a novel method combining modified non-negative matrix factorization and adaptive filtering. This extracts clean heart sounds while addressing interference of body sounds and audio produced by the earphones. We further explore the uniqueness of IEM-recorded heart sounds in three aspects to extract a novel biometric representation, based on which HeartPrint leverages a convolutional neural model equipped with a continual learning method to achieve accurate authentication under drifting body conditions. Furthermore, user-friendly registration and energy-effective authentication are facilitated by a data augmentation method using transformer-based GAN and an authentication interval control method. Extensive experiments with 45 participants confirm that HeartPrint can achieve 1.6\% FAR and 1.8\% FRR, while effectively coping with major attacks, complicated interference, and hardware diversity, while exhibiting robustness in real-world environments.},
+ number = {2},
+ urldate = {2025-11-28},
+ journal = {10.1109/INFOCOM53939.2023.10228921},
+ author = {Cao, Yetong and Cai, Chao and Li, Fan and Chen, Zhe and Luo, Jun},
+ month = mar,
+ year = {2025},
+ keywords = {Ear, Authentication, Headphones, Heart, Biometrics (access control), ANC earphones, Bones, in-ear microphones, neural network, Passive authentication, Phonocardiography},
+ pages = {1195--1209},
+ file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\G65NY2B6\\Cao et al. - 2025 - Enabling Passive User Authentication via Heart Sounds on In-Ear Microphones.pdf:application/pdf},
+}</t>
+  </si>
+  <si>
+    <t>@article{amesaka_earlock_2025,
+ title = {{EarLock}: {Personal} {Authentication} {System} for {Hearables} {Using} {Sound} {Leakage} {Signals}},
+ volume = {24},
+ issn = {1558-0660},
+ shorttitle = {{EarLock}},
+ url = {https://ieeexplore.ieee.org/document/10879366},
+ doi = {10.1109/TMC.2025.3540584},
+ abstract = {Earphone-type wearable devices, also known as “hearables,” will have many functions in the future. Some of those functions will require authentication of the wearer for access to the user's privacy information or settlement of payments. In this study, we propose a new personal authentication system for hearables called EarLock. EarLock authenticates the wearer by acquiring and analyzing ear canal and auricle shape information using sound leakage from the device. The system can be implemented using a speaker and external microphone that are highly compatible with hearables. We implemented three prototype devices and investigated EarLock's authentication performance under various practical scenarios, including walking conditions, noisy environments, and situations with object interference. Experimental results showed that the in-ear, open-ear, and bone-conduction devices achieved balanced accuracy (BAC) scores of 87.2–93.7\%, 83.4–94.7\%, and 85.9–90.0\%.},
+ number = {7},
+ urldate = {2025-11-28},
+ journal = {IEEE Transactions on Mobile Computing},
+ author = {Amesaka, Takashi and Watanabe, Hiroki and Sugiura, Yuta and Sugimoto, Masanori and Shizuki, Buntarou},
+ month = jul,
+ year = {2025},
+ keywords = {Ear, Irrigation, Authentication, Electroencephalography, Biometrics, Shape, Microphones, Acoustics, authentication, active acoustic sensing, ear biometrics, Hearables, Legged locomotion, Mobile computing, sound leakage},
+ pages = {6183--6196},
+ file = {Full Text PDF:C\:\\Users\\ysj28\\Zotero\\storage\\6V24CG7D\\Amesaka et al. - 2025 - EarLock Personal Authentication System for Hearables Using Sound Leakage Signals.pdf:application/pdf},
 }</t>
   </si>
   <si>
@@ -1931,19 +1930,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" ht="409.5" spans="1:2">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" ht="409.5" spans="1:2">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>3</v>
       </c>
     </row>
@@ -1951,229 +1950,229 @@
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" ht="395.2" spans="1:2">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" ht="409.5" spans="1:2">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" ht="409.5" spans="1:2">
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" ht="409.5" spans="1:2">
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" ht="409.5" spans="1:2">
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" ht="409.5" spans="1:2">
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" ht="366.4" spans="1:2">
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" ht="409.5" spans="1:2">
       <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" ht="409.5" spans="1:2">
       <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" ht="409.5" spans="1:2">
       <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" ht="409.5" spans="1:2">
       <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" ht="409.5" spans="1:2">
       <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" ht="409.5" spans="1:2">
       <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" ht="409.5" spans="1:2">
       <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" ht="409.5" spans="1:2">
       <c r="A19">
         <v>18</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" ht="409.5" spans="1:2">
       <c r="A20">
         <v>19</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" ht="409.5" spans="1:2">
       <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" ht="409.5" spans="1:2">
       <c r="A22">
         <v>21</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" ht="409.5" spans="1:2">
       <c r="A23">
         <v>22</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" ht="409.5" spans="1:2">
       <c r="A24">
         <v>23</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" ht="409.5" spans="1:2">
       <c r="A25">
         <v>24</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" ht="409.5" spans="1:2">
       <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B26" t="s">
+    </row>
+    <row r="27" ht="409.5" spans="1:2">
+      <c r="A27">
         <v>26</v>
       </c>
-    </row>
-    <row r="27" spans="1:2">
-      <c r="A27">
+      <c r="B27" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B27" t="s">
+    </row>
+    <row r="28" ht="409.5" spans="1:2">
+      <c r="A28">
         <v>27</v>
       </c>
-    </row>
-    <row r="28" spans="1:2">
-      <c r="A28">
+      <c r="B28" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B28" t="s">
+    </row>
+    <row r="29" ht="409.5" spans="1:2">
+      <c r="A29">
         <v>28</v>
       </c>
-    </row>
-    <row r="29" spans="1:2">
-      <c r="A29">
+      <c r="B29" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B29" t="s">
+    </row>
+    <row r="30" ht="409.5" spans="1:2">
+      <c r="A30">
         <v>29</v>
       </c>
-    </row>
-    <row r="30" spans="1:2">
-      <c r="A30">
-        <v>31</v>
-      </c>
-      <c r="B30" t="s">
+      <c r="B30" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="31" spans="1:2">
+    <row r="31" ht="409.5" spans="1:2">
       <c r="A31">
-        <v>32</v>
-      </c>
-      <c r="B31" t="s">
+        <v>30</v>
+      </c>
+      <c r="B31" s="2" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="32" ht="409.5" spans="1:2">
       <c r="A32">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>32</v>
@@ -2181,7 +2180,7 @@
     </row>
     <row r="33" ht="409.5" spans="1:2">
       <c r="A33">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>33</v>
@@ -2189,7 +2188,7 @@
     </row>
     <row r="34" ht="409.5" spans="1:2">
       <c r="A34">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>34</v>
@@ -2197,7 +2196,7 @@
     </row>
     <row r="35" ht="409.5" spans="1:2">
       <c r="A35">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>35</v>
@@ -2205,7 +2204,7 @@
     </row>
     <row r="36" ht="409.5" spans="1:2">
       <c r="A36">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>36</v>
@@ -2213,7 +2212,7 @@
     </row>
     <row r="37" ht="409.5" spans="1:2">
       <c r="A37">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>37</v>
@@ -2221,7 +2220,7 @@
     </row>
     <row r="38" ht="409.5" spans="1:2">
       <c r="A38">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>38</v>
@@ -2229,7 +2228,7 @@
     </row>
     <row r="39" ht="409.5" spans="1:2">
       <c r="A39">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>39</v>
@@ -2237,15 +2236,15 @@
     </row>
     <row r="40" ht="409.5" spans="1:2">
       <c r="A40">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="41" ht="409.5" spans="1:2">
+    <row r="41" ht="84.8" spans="1:2">
       <c r="A41">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>41</v>
@@ -2253,15 +2252,15 @@
     </row>
     <row r="42" ht="409.5" spans="1:2">
       <c r="A42">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="43" ht="395.2" spans="1:2">
+    <row r="43" ht="409.5" spans="1:2">
       <c r="A43">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>43</v>
@@ -2269,15 +2268,15 @@
     </row>
     <row r="44" ht="409.5" spans="1:2">
       <c r="A44">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="45" ht="366.4" spans="1:2">
+    <row r="45" ht="409.5" spans="1:2">
       <c r="A45">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>45</v>
@@ -2285,7 +2284,7 @@
     </row>
     <row r="46" ht="409.5" spans="1:2">
       <c r="A46">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>46</v>
@@ -2293,7 +2292,7 @@
     </row>
     <row r="47" ht="409.5" spans="1:2">
       <c r="A47">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>47</v>
